--- a/Lab Session 1/Lab Session 1.xlsx
+++ b/Lab Session 1/Lab Session 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\siddi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NED University\GitHub\Artificial-Intelligence-CS-323\Lab Session 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0912B40-1DDC-4F76-9F57-1FF5BF7C9956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF5BA73-855B-4A27-A8E7-5AD51F37276E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="844" firstSheet="3" activeTab="8" xr2:uid="{26A035F0-FBB6-49CB-9627-A112974C9DEA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="844" activeTab="6" xr2:uid="{26A035F0-FBB6-49CB-9627-A112974C9DEA}"/>
   </bookViews>
   <sheets>
     <sheet name="OR Gate Training" sheetId="2" r:id="rId1"/>
@@ -489,7 +489,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -508,15 +508,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -524,30 +515,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -568,7 +535,39 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="40% - Accent4" xfId="2" builtinId="43"/>
@@ -941,7 +940,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="18">
+      <c r="A2" s="35">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -990,7 +989,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
+      <c r="A3" s="36"/>
       <c r="B3">
         <v>0</v>
       </c>
@@ -1039,7 +1038,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="19"/>
+      <c r="A4" s="36"/>
       <c r="B4">
         <v>1</v>
       </c>
@@ -1088,7 +1087,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
+      <c r="A5" s="37"/>
       <c r="B5">
         <v>1</v>
       </c>
@@ -1137,7 +1136,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
+      <c r="A6" s="35">
         <v>2</v>
       </c>
       <c r="B6" s="1">
@@ -1188,7 +1187,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
+      <c r="A7" s="36"/>
       <c r="B7">
         <v>0</v>
       </c>
@@ -1237,7 +1236,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
+      <c r="A8" s="36"/>
       <c r="B8">
         <v>1</v>
       </c>
@@ -1286,7 +1285,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
+      <c r="A9" s="37"/>
       <c r="B9">
         <v>1</v>
       </c>
@@ -1335,7 +1334,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="18">
+      <c r="A10" s="35">
         <v>3</v>
       </c>
       <c r="B10" s="1">
@@ -1386,7 +1385,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="19"/>
+      <c r="A11" s="36"/>
       <c r="B11">
         <v>0</v>
       </c>
@@ -1435,7 +1434,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="19"/>
+      <c r="A12" s="36"/>
       <c r="B12">
         <v>1</v>
       </c>
@@ -1484,7 +1483,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
+      <c r="A13" s="37"/>
       <c r="B13">
         <v>1</v>
       </c>
@@ -1533,7 +1532,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="18">
+      <c r="A14" s="35">
         <v>4</v>
       </c>
       <c r="B14" s="1">
@@ -1584,7 +1583,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="19"/>
+      <c r="A15" s="36"/>
       <c r="B15">
         <v>0</v>
       </c>
@@ -1633,7 +1632,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="19"/>
+      <c r="A16" s="36"/>
       <c r="B16">
         <v>1</v>
       </c>
@@ -1682,7 +1681,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="20"/>
+      <c r="A17" s="37"/>
       <c r="B17">
         <v>1</v>
       </c>
@@ -1731,7 +1730,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="18">
+      <c r="A18" s="35">
         <v>5</v>
       </c>
       <c r="B18" s="1">
@@ -1782,7 +1781,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
+      <c r="A19" s="36"/>
       <c r="B19">
         <v>0</v>
       </c>
@@ -1831,7 +1830,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="19"/>
+      <c r="A20" s="36"/>
       <c r="B20">
         <v>1</v>
       </c>
@@ -1880,7 +1879,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="20"/>
+      <c r="A21" s="37"/>
       <c r="B21" s="4">
         <v>1</v>
       </c>
@@ -1946,22 +1945,22 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="34"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="23"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -2008,7 +2007,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="21">
+      <c r="A3" s="18">
         <v>1</v>
       </c>
       <c r="B3" s="1">
@@ -2057,7 +2056,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
+      <c r="A4" s="19"/>
       <c r="B4">
         <v>0</v>
       </c>
@@ -2106,7 +2105,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
+      <c r="A5" s="19"/>
       <c r="B5">
         <v>1</v>
       </c>
@@ -2155,7 +2154,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="23"/>
+      <c r="A6" s="20"/>
       <c r="B6" s="4">
         <v>1</v>
       </c>
@@ -2204,7 +2203,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="21">
+      <c r="A7" s="18">
         <v>2</v>
       </c>
       <c r="B7" s="1">
@@ -2255,7 +2254,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
+      <c r="A8" s="19"/>
       <c r="B8">
         <v>0</v>
       </c>
@@ -2304,7 +2303,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
+      <c r="A9" s="19"/>
       <c r="B9">
         <v>1</v>
       </c>
@@ -2353,7 +2352,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
+      <c r="A10" s="19"/>
       <c r="B10">
         <v>1</v>
       </c>
@@ -2402,7 +2401,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="21">
+      <c r="A11" s="18">
         <v>3</v>
       </c>
       <c r="B11" s="1">
@@ -2453,7 +2452,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12">
         <v>0</v>
       </c>
@@ -2502,7 +2501,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
+      <c r="A13" s="19"/>
       <c r="B13">
         <v>1</v>
       </c>
@@ -2551,7 +2550,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
+      <c r="A14" s="19"/>
       <c r="B14">
         <v>1</v>
       </c>
@@ -2600,7 +2599,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="21">
+      <c r="A15" s="18">
         <v>4</v>
       </c>
       <c r="B15" s="1">
@@ -2651,7 +2650,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
+      <c r="A16" s="19"/>
       <c r="B16">
         <v>0</v>
       </c>
@@ -2700,7 +2699,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="22"/>
+      <c r="A17" s="19"/>
       <c r="B17">
         <v>1</v>
       </c>
@@ -2749,7 +2748,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="23"/>
+      <c r="A18" s="20"/>
       <c r="B18" s="4">
         <v>1</v>
       </c>
@@ -2798,22 +2797,22 @@
       </c>
     </row>
     <row r="20" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="34"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="23"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
@@ -2860,7 +2859,7 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="21">
+      <c r="A22" s="18">
         <v>1</v>
       </c>
       <c r="B22" s="1">
@@ -2909,7 +2908,7 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="22"/>
+      <c r="A23" s="19"/>
       <c r="B23">
         <v>0</v>
       </c>
@@ -2958,7 +2957,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="22"/>
+      <c r="A24" s="19"/>
       <c r="B24">
         <v>1</v>
       </c>
@@ -3007,7 +3006,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="23"/>
+      <c r="A25" s="20"/>
       <c r="B25" s="4">
         <v>1</v>
       </c>
@@ -3056,7 +3055,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="21">
+      <c r="A26" s="18">
         <v>2</v>
       </c>
       <c r="B26" s="1">
@@ -3107,7 +3106,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="22"/>
+      <c r="A27" s="19"/>
       <c r="B27">
         <v>0</v>
       </c>
@@ -3156,7 +3155,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="22"/>
+      <c r="A28" s="19"/>
       <c r="B28">
         <v>1</v>
       </c>
@@ -3205,7 +3204,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="23"/>
+      <c r="A29" s="20"/>
       <c r="B29" s="4">
         <v>1</v>
       </c>
@@ -3254,7 +3253,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="21">
+      <c r="A30" s="18">
         <v>3</v>
       </c>
       <c r="B30" s="1">
@@ -3305,7 +3304,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="22"/>
+      <c r="A31" s="19"/>
       <c r="B31">
         <v>0</v>
       </c>
@@ -3354,7 +3353,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="22"/>
+      <c r="A32" s="19"/>
       <c r="B32">
         <v>1</v>
       </c>
@@ -3403,7 +3402,7 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="23"/>
+      <c r="A33" s="20"/>
       <c r="B33" s="4">
         <v>1</v>
       </c>
@@ -3452,7 +3451,7 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="21">
+      <c r="A34" s="18">
         <v>4</v>
       </c>
       <c r="B34" s="1">
@@ -3503,7 +3502,7 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="22"/>
+      <c r="A35" s="19"/>
       <c r="B35">
         <v>0</v>
       </c>
@@ -3552,7 +3551,7 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="22"/>
+      <c r="A36" s="19"/>
       <c r="B36">
         <v>1</v>
       </c>
@@ -3601,7 +3600,7 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="22"/>
+      <c r="A37" s="19"/>
       <c r="B37">
         <v>1</v>
       </c>
@@ -3650,7 +3649,7 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="21">
+      <c r="A38" s="18">
         <v>5</v>
       </c>
       <c r="B38" s="1">
@@ -3701,7 +3700,7 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="22"/>
+      <c r="A39" s="19"/>
       <c r="B39">
         <v>0</v>
       </c>
@@ -3750,7 +3749,7 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="22"/>
+      <c r="A40" s="19"/>
       <c r="B40">
         <v>1</v>
       </c>
@@ -3799,7 +3798,7 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="23"/>
+      <c r="A41" s="20"/>
       <c r="B41" s="4">
         <v>1</v>
       </c>
@@ -3848,22 +3847,22 @@
       </c>
     </row>
     <row r="43" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B43" s="33"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="33"/>
-      <c r="M43" s="33"/>
-      <c r="N43" s="34"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="22"/>
+      <c r="N43" s="23"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
@@ -3910,7 +3909,7 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="35">
+      <c r="A45" s="24">
         <v>1</v>
       </c>
       <c r="B45" s="1">
@@ -3959,7 +3958,7 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="36"/>
+      <c r="A46" s="25"/>
       <c r="B46">
         <v>0</v>
       </c>
@@ -4008,7 +4007,7 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="36"/>
+      <c r="A47" s="25"/>
       <c r="B47">
         <v>0</v>
       </c>
@@ -4057,7 +4056,7 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
+      <c r="A48" s="26"/>
       <c r="B48" s="4">
         <v>1</v>
       </c>
@@ -4107,11 +4106,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A41"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="A20:N20"/>
@@ -4120,6 +4114,11 @@
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4175,7 +4174,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="18">
+      <c r="A2" s="35">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -4224,7 +4223,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
+      <c r="A3" s="36"/>
       <c r="B3">
         <v>0</v>
       </c>
@@ -4273,7 +4272,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="19"/>
+      <c r="A4" s="36"/>
       <c r="B4">
         <v>1</v>
       </c>
@@ -4322,7 +4321,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
+      <c r="A5" s="37"/>
       <c r="B5">
         <v>1</v>
       </c>
@@ -4371,7 +4370,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
+      <c r="A6" s="35">
         <v>2</v>
       </c>
       <c r="B6" s="1">
@@ -4422,7 +4421,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
+      <c r="A7" s="36"/>
       <c r="B7">
         <v>0</v>
       </c>
@@ -4471,7 +4470,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
+      <c r="A8" s="36"/>
       <c r="B8">
         <v>1</v>
       </c>
@@ -4520,7 +4519,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
+      <c r="A9" s="37"/>
       <c r="B9">
         <v>1</v>
       </c>
@@ -4569,7 +4568,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="18">
+      <c r="A10" s="35">
         <v>3</v>
       </c>
       <c r="B10" s="1">
@@ -4620,7 +4619,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="19"/>
+      <c r="A11" s="36"/>
       <c r="B11">
         <v>0</v>
       </c>
@@ -4669,7 +4668,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="19"/>
+      <c r="A12" s="36"/>
       <c r="B12">
         <v>1</v>
       </c>
@@ -4718,7 +4717,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
+      <c r="A13" s="37"/>
       <c r="B13">
         <v>1</v>
       </c>
@@ -4767,7 +4766,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="18">
+      <c r="A14" s="35">
         <v>4</v>
       </c>
       <c r="B14" s="1">
@@ -4818,7 +4817,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="19"/>
+      <c r="A15" s="36"/>
       <c r="B15">
         <v>0</v>
       </c>
@@ -4867,7 +4866,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="19"/>
+      <c r="A16" s="36"/>
       <c r="B16">
         <v>1</v>
       </c>
@@ -4916,7 +4915,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="20"/>
+      <c r="A17" s="37"/>
       <c r="B17">
         <v>1</v>
       </c>
@@ -4965,7 +4964,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="18">
+      <c r="A18" s="35">
         <v>5</v>
       </c>
       <c r="B18" s="1">
@@ -5016,7 +5015,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
+      <c r="A19" s="36"/>
       <c r="B19">
         <v>0</v>
       </c>
@@ -5065,7 +5064,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="19"/>
+      <c r="A20" s="36"/>
       <c r="B20">
         <v>1</v>
       </c>
@@ -5114,7 +5113,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="20"/>
+      <c r="A21" s="37"/>
       <c r="B21" s="4">
         <v>1</v>
       </c>
@@ -5224,7 +5223,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="21">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -5273,7 +5272,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
+      <c r="A3" s="19"/>
       <c r="B3">
         <v>0</v>
       </c>
@@ -5322,7 +5321,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
+      <c r="A4" s="19"/>
       <c r="B4">
         <v>1</v>
       </c>
@@ -5371,7 +5370,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
+      <c r="A5" s="20"/>
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -5420,7 +5419,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
+      <c r="A6" s="18">
         <v>2</v>
       </c>
       <c r="B6" s="1">
@@ -5471,7 +5470,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
+      <c r="A7" s="19"/>
       <c r="B7">
         <v>0</v>
       </c>
@@ -5520,7 +5519,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
+      <c r="A8" s="19"/>
       <c r="B8">
         <v>1</v>
       </c>
@@ -5569,7 +5568,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
+      <c r="A9" s="19"/>
       <c r="B9">
         <v>1</v>
       </c>
@@ -5618,7 +5617,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
+      <c r="A10" s="18">
         <v>3</v>
       </c>
       <c r="B10" s="1">
@@ -5669,7 +5668,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
+      <c r="A11" s="19"/>
       <c r="B11">
         <v>0</v>
       </c>
@@ -5718,7 +5717,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12">
         <v>1</v>
       </c>
@@ -5767,7 +5766,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
+      <c r="A13" s="19"/>
       <c r="B13">
         <v>1</v>
       </c>
@@ -5816,7 +5815,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="21">
+      <c r="A14" s="18">
         <v>4</v>
       </c>
       <c r="B14" s="1">
@@ -5867,7 +5866,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
+      <c r="A15" s="19"/>
       <c r="B15">
         <v>0</v>
       </c>
@@ -5916,7 +5915,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
+      <c r="A16" s="19"/>
       <c r="B16">
         <v>1</v>
       </c>
@@ -5965,7 +5964,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="23"/>
+      <c r="A17" s="20"/>
       <c r="B17" s="4">
         <v>1</v>
       </c>
@@ -6074,7 +6073,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="21">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -6123,7 +6122,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
+      <c r="A3" s="19"/>
       <c r="B3">
         <v>0</v>
       </c>
@@ -6172,7 +6171,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
+      <c r="A4" s="19"/>
       <c r="B4">
         <v>1</v>
       </c>
@@ -6221,7 +6220,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
+      <c r="A5" s="20"/>
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -6270,7 +6269,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
+      <c r="A6" s="18">
         <v>2</v>
       </c>
       <c r="B6" s="1">
@@ -6321,7 +6320,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
+      <c r="A7" s="19"/>
       <c r="B7">
         <v>0</v>
       </c>
@@ -6370,7 +6369,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
+      <c r="A8" s="19"/>
       <c r="B8">
         <v>1</v>
       </c>
@@ -6419,7 +6418,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
+      <c r="A9" s="20"/>
       <c r="B9" s="4">
         <v>1</v>
       </c>
@@ -6468,7 +6467,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
+      <c r="A10" s="18">
         <v>3</v>
       </c>
       <c r="B10" s="1">
@@ -6519,7 +6518,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
+      <c r="A11" s="19"/>
       <c r="B11">
         <v>0</v>
       </c>
@@ -6568,7 +6567,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12">
         <v>1</v>
       </c>
@@ -6617,7 +6616,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="23"/>
+      <c r="A13" s="20"/>
       <c r="B13" s="4">
         <v>1</v>
       </c>
@@ -6666,7 +6665,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="21">
+      <c r="A14" s="18">
         <v>4</v>
       </c>
       <c r="B14" s="1">
@@ -6717,7 +6716,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
+      <c r="A15" s="19"/>
       <c r="B15">
         <v>0</v>
       </c>
@@ -6766,7 +6765,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
+      <c r="A16" s="19"/>
       <c r="B16">
         <v>1</v>
       </c>
@@ -6815,7 +6814,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="23"/>
+      <c r="A17" s="20"/>
       <c r="B17" s="4">
         <v>1</v>
       </c>
@@ -6864,7 +6863,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="21">
+      <c r="A18" s="18">
         <v>5</v>
       </c>
       <c r="B18" s="1">
@@ -6915,7 +6914,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="22"/>
+      <c r="A19" s="19"/>
       <c r="B19">
         <v>0</v>
       </c>
@@ -6964,7 +6963,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="22"/>
+      <c r="A20" s="19"/>
       <c r="B20">
         <v>1</v>
       </c>
@@ -7013,7 +7012,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="23"/>
+      <c r="A21" s="20"/>
       <c r="B21" s="4">
         <v>1</v>
       </c>
@@ -7062,7 +7061,7 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="21">
+      <c r="A22" s="18">
         <v>6</v>
       </c>
       <c r="B22" s="1">
@@ -7113,7 +7112,7 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="22"/>
+      <c r="A23" s="19"/>
       <c r="B23">
         <v>0</v>
       </c>
@@ -7162,7 +7161,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="22"/>
+      <c r="A24" s="19"/>
       <c r="B24">
         <v>1</v>
       </c>
@@ -7211,7 +7210,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="23"/>
+      <c r="A25" s="20"/>
       <c r="B25" s="4">
         <v>1</v>
       </c>
@@ -7260,7 +7259,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="21">
+      <c r="A26" s="18">
         <v>7</v>
       </c>
       <c r="B26" s="1">
@@ -7311,7 +7310,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="22"/>
+      <c r="A27" s="19"/>
       <c r="B27">
         <v>0</v>
       </c>
@@ -7360,7 +7359,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="22"/>
+      <c r="A28" s="19"/>
       <c r="B28">
         <v>1</v>
       </c>
@@ -7409,7 +7408,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="23"/>
+      <c r="A29" s="20"/>
       <c r="B29" s="4">
         <v>1</v>
       </c>
@@ -7458,7 +7457,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="21">
+      <c r="A30" s="18">
         <v>8</v>
       </c>
       <c r="B30" s="1">
@@ -7509,7 +7508,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="22"/>
+      <c r="A31" s="19"/>
       <c r="B31">
         <v>0</v>
       </c>
@@ -7558,7 +7557,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="22"/>
+      <c r="A32" s="19"/>
       <c r="B32">
         <v>1</v>
       </c>
@@ -7607,7 +7606,7 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="23"/>
+      <c r="A33" s="20"/>
       <c r="B33" s="4">
         <v>1</v>
       </c>
@@ -7656,7 +7655,7 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="21">
+      <c r="A34" s="18">
         <v>9</v>
       </c>
       <c r="B34" s="1">
@@ -7707,7 +7706,7 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="22"/>
+      <c r="A35" s="19"/>
       <c r="B35">
         <v>0</v>
       </c>
@@ -7756,7 +7755,7 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="22"/>
+      <c r="A36" s="19"/>
       <c r="B36">
         <v>1</v>
       </c>
@@ -7805,7 +7804,7 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="23"/>
+      <c r="A37" s="20"/>
       <c r="B37" s="4">
         <v>1</v>
       </c>
@@ -7854,7 +7853,7 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="21">
+      <c r="A38" s="18">
         <v>10</v>
       </c>
       <c r="B38" s="1">
@@ -7905,7 +7904,7 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="22"/>
+      <c r="A39" s="19"/>
       <c r="B39">
         <v>0</v>
       </c>
@@ -7954,7 +7953,7 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="22"/>
+      <c r="A40" s="19"/>
       <c r="B40">
         <v>1</v>
       </c>
@@ -8003,7 +8002,7 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="23"/>
+      <c r="A41" s="20"/>
       <c r="B41" s="4">
         <v>1</v>
       </c>
@@ -8052,7 +8051,7 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="21">
+      <c r="A42" s="18">
         <v>11</v>
       </c>
       <c r="B42" s="1">
@@ -8103,7 +8102,7 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="22"/>
+      <c r="A43" s="19"/>
       <c r="B43">
         <v>0</v>
       </c>
@@ -8152,7 +8151,7 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="22"/>
+      <c r="A44" s="19"/>
       <c r="B44">
         <v>1</v>
       </c>
@@ -8201,7 +8200,7 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="23"/>
+      <c r="A45" s="20"/>
       <c r="B45" s="4">
         <v>1</v>
       </c>
@@ -8250,7 +8249,7 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="21">
+      <c r="A46" s="18">
         <v>12</v>
       </c>
       <c r="B46" s="1">
@@ -8301,7 +8300,7 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="22"/>
+      <c r="A47" s="19"/>
       <c r="B47">
         <v>0</v>
       </c>
@@ -8350,7 +8349,7 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="22"/>
+      <c r="A48" s="19"/>
       <c r="B48">
         <v>1</v>
       </c>
@@ -8399,7 +8398,7 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="23"/>
+      <c r="A49" s="20"/>
       <c r="B49" s="4">
         <v>1</v>
       </c>
@@ -8448,7 +8447,7 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="21">
+      <c r="A50" s="18">
         <v>13</v>
       </c>
       <c r="B50" s="1">
@@ -8499,7 +8498,7 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="22"/>
+      <c r="A51" s="19"/>
       <c r="B51">
         <v>0</v>
       </c>
@@ -8548,7 +8547,7 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="22"/>
+      <c r="A52" s="19"/>
       <c r="B52">
         <v>1</v>
       </c>
@@ -8597,7 +8596,7 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="23"/>
+      <c r="A53" s="20"/>
       <c r="B53" s="4">
         <v>1</v>
       </c>
@@ -8646,7 +8645,7 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="21">
+      <c r="A54" s="18">
         <v>14</v>
       </c>
       <c r="B54" s="1">
@@ -8697,7 +8696,7 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="22"/>
+      <c r="A55" s="19"/>
       <c r="B55">
         <v>0</v>
       </c>
@@ -8746,7 +8745,7 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="22"/>
+      <c r="A56" s="19"/>
       <c r="B56">
         <v>1</v>
       </c>
@@ -8795,7 +8794,7 @@
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="23"/>
+      <c r="A57" s="20"/>
       <c r="B57" s="4">
         <v>1</v>
       </c>
@@ -8845,12 +8844,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
     <mergeCell ref="A50:A53"/>
     <mergeCell ref="A54:A57"/>
     <mergeCell ref="A26:A29"/>
@@ -8859,6 +8852,12 @@
     <mergeCell ref="A38:A41"/>
     <mergeCell ref="A42:A45"/>
     <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8914,7 +8913,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="21">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -8963,7 +8962,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
+      <c r="A3" s="19"/>
       <c r="B3">
         <v>0</v>
       </c>
@@ -9012,7 +9011,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
+      <c r="A4" s="19"/>
       <c r="B4">
         <v>1</v>
       </c>
@@ -9061,7 +9060,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
+      <c r="A5" s="20"/>
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -9110,7 +9109,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
+      <c r="A6" s="18">
         <v>2</v>
       </c>
       <c r="B6" s="1">
@@ -9161,7 +9160,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
+      <c r="A7" s="19"/>
       <c r="B7">
         <v>0</v>
       </c>
@@ -9210,7 +9209,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
+      <c r="A8" s="19"/>
       <c r="B8">
         <v>1</v>
       </c>
@@ -9259,7 +9258,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
+      <c r="A9" s="20"/>
       <c r="B9" s="4">
         <v>1</v>
       </c>
@@ -9308,7 +9307,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
+      <c r="A10" s="18">
         <v>3</v>
       </c>
       <c r="B10" s="1">
@@ -9359,7 +9358,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
+      <c r="A11" s="19"/>
       <c r="B11">
         <v>0</v>
       </c>
@@ -9408,7 +9407,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12">
         <v>1</v>
       </c>
@@ -9457,7 +9456,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="23"/>
+      <c r="A13" s="20"/>
       <c r="B13" s="4">
         <v>1</v>
       </c>
@@ -9506,7 +9505,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="21">
+      <c r="A14" s="18">
         <v>4</v>
       </c>
       <c r="B14" s="1">
@@ -9557,7 +9556,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
+      <c r="A15" s="19"/>
       <c r="B15">
         <v>0</v>
       </c>
@@ -9606,7 +9605,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
+      <c r="A16" s="19"/>
       <c r="B16">
         <v>1</v>
       </c>
@@ -9655,7 +9654,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="22"/>
+      <c r="A17" s="19"/>
       <c r="B17">
         <v>1</v>
       </c>
@@ -9704,7 +9703,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="21">
+      <c r="A18" s="18">
         <v>5</v>
       </c>
       <c r="B18" s="1">
@@ -9755,7 +9754,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="22"/>
+      <c r="A19" s="19"/>
       <c r="B19">
         <v>0</v>
       </c>
@@ -9804,7 +9803,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="22"/>
+      <c r="A20" s="19"/>
       <c r="B20">
         <v>1</v>
       </c>
@@ -9853,7 +9852,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="23"/>
+      <c r="A21" s="20"/>
       <c r="B21" s="4">
         <v>1</v>
       </c>
@@ -9972,7 +9971,7 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="18">
+      <c r="A2" s="35">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -10031,7 +10030,7 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
+      <c r="A3" s="36"/>
       <c r="B3">
         <v>0</v>
       </c>
@@ -10091,7 +10090,7 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="19"/>
+      <c r="A4" s="36"/>
       <c r="B4">
         <v>0</v>
       </c>
@@ -10151,7 +10150,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
+      <c r="A5" s="36"/>
       <c r="B5">
         <v>0</v>
       </c>
@@ -10211,7 +10210,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="19"/>
+      <c r="A6" s="36"/>
       <c r="B6">
         <v>1</v>
       </c>
@@ -10271,7 +10270,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
+      <c r="A7" s="36"/>
       <c r="B7">
         <v>1</v>
       </c>
@@ -10331,7 +10330,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
+      <c r="A8" s="36"/>
       <c r="B8">
         <v>1</v>
       </c>
@@ -10391,59 +10390,59 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="38">
-        <v>1</v>
-      </c>
-      <c r="C9" s="38">
-        <v>1</v>
-      </c>
-      <c r="D9" s="38">
-        <v>1</v>
-      </c>
-      <c r="E9" s="38">
-        <v>1</v>
-      </c>
-      <c r="F9" s="38">
+      <c r="A9" s="36"/>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="I9" s="38">
+      <c r="I9">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="J9" s="38">
+      <c r="J9">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K9" s="38">
+      <c r="K9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L9" s="38">
+      <c r="L9">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="M9" s="38">
+      <c r="M9">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="N9" s="38">
+      <c r="N9">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="O9" s="38">
-        <v>0</v>
-      </c>
-      <c r="P9" s="38">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
         <v>0.1</v>
       </c>
       <c r="Q9" s="3">
@@ -10451,7 +10450,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="35">
+      <c r="A10" s="24">
         <v>2</v>
       </c>
       <c r="B10" s="1">
@@ -10513,59 +10512,59 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="38">
-        <v>0</v>
-      </c>
-      <c r="C11" s="38">
-        <v>0</v>
-      </c>
-      <c r="D11" s="38">
-        <v>1</v>
-      </c>
-      <c r="E11" s="38">
-        <v>1</v>
-      </c>
-      <c r="F11" s="38">
+      <c r="A11" s="25"/>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="I11" s="38">
+      <c r="I11">
         <f t="shared" ref="I11:I17" si="12">B11*F11+C11*G11+D11*H11+O11</f>
         <v>1</v>
       </c>
-      <c r="J11" s="38">
+      <c r="J11">
         <f t="shared" ref="J11:J17" si="13">IF(I11&gt;Q11,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K11" s="38">
+      <c r="K11">
         <f t="shared" ref="K11:K17" si="14">E11-J11</f>
         <v>0</v>
       </c>
-      <c r="L11" s="38">
+      <c r="L11">
         <f t="shared" ref="L11:L17" si="15">F11+(P11*K11*B11)</f>
         <v>1</v>
       </c>
-      <c r="M11" s="38">
+      <c r="M11">
         <f t="shared" ref="M11:M17" si="16">F11+(P11*K11*C11)</f>
         <v>1</v>
       </c>
-      <c r="N11" s="38">
+      <c r="N11">
         <f t="shared" ref="N11:N17" si="17">F11+(P11*K11*D11)</f>
         <v>1</v>
       </c>
-      <c r="O11" s="38">
-        <v>0</v>
-      </c>
-      <c r="P11" s="38">
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
         <v>0.1</v>
       </c>
       <c r="Q11" s="3">
@@ -10573,59 +10572,59 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
-      <c r="B12" s="38">
-        <v>0</v>
-      </c>
-      <c r="C12" s="38">
-        <v>1</v>
-      </c>
-      <c r="D12" s="38">
-        <v>0</v>
-      </c>
-      <c r="E12" s="38">
-        <v>1</v>
-      </c>
-      <c r="F12" s="38">
+      <c r="A12" s="25"/>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="G12" s="38">
+      <c r="G12">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="I12" s="38">
+      <c r="I12">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="J12" s="38">
+      <c r="J12">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="K12" s="38">
+      <c r="K12">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L12" s="38">
+      <c r="L12">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="M12" s="38">
+      <c r="M12">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="N12" s="38">
+      <c r="N12">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O12" s="38">
-        <v>0</v>
-      </c>
-      <c r="P12" s="38">
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
         <v>0.1</v>
       </c>
       <c r="Q12" s="3">
@@ -10633,59 +10632,59 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="38">
-        <v>0</v>
-      </c>
-      <c r="C13" s="38">
-        <v>1</v>
-      </c>
-      <c r="D13" s="38">
-        <v>1</v>
-      </c>
-      <c r="E13" s="38">
-        <v>1</v>
-      </c>
-      <c r="F13" s="38">
+      <c r="A13" s="25"/>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="I13" s="38">
+      <c r="I13">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="J13" s="38">
+      <c r="J13">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="K13" s="38">
+      <c r="K13">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L13" s="38">
+      <c r="L13">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="M13" s="38">
+      <c r="M13">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="N13" s="38">
+      <c r="N13">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O13" s="38">
-        <v>0</v>
-      </c>
-      <c r="P13" s="38">
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
         <v>0.1</v>
       </c>
       <c r="Q13" s="3">
@@ -10693,59 +10692,59 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
-      <c r="B14" s="38">
-        <v>1</v>
-      </c>
-      <c r="C14" s="38">
-        <v>0</v>
-      </c>
-      <c r="D14" s="38">
-        <v>0</v>
-      </c>
-      <c r="E14" s="38">
-        <v>1</v>
-      </c>
-      <c r="F14" s="38">
+      <c r="A14" s="25"/>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="I14" s="38">
+      <c r="I14">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="J14" s="38">
+      <c r="J14">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="K14" s="38">
+      <c r="K14">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L14" s="38">
+      <c r="L14">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="M14" s="38">
+      <c r="M14">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="N14" s="38">
+      <c r="N14">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O14" s="38">
-        <v>0</v>
-      </c>
-      <c r="P14" s="38">
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
         <v>0.1</v>
       </c>
       <c r="Q14" s="3">
@@ -10753,59 +10752,59 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="36"/>
-      <c r="B15" s="38">
-        <v>1</v>
-      </c>
-      <c r="C15" s="38">
-        <v>0</v>
-      </c>
-      <c r="D15" s="38">
-        <v>1</v>
-      </c>
-      <c r="E15" s="38">
-        <v>1</v>
-      </c>
-      <c r="F15" s="38">
+      <c r="A15" s="25"/>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="G15" s="38">
+      <c r="G15">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="H15" s="38">
+      <c r="H15">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="I15" s="38">
+      <c r="I15">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="J15" s="38">
+      <c r="J15">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="K15" s="38">
+      <c r="K15">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L15" s="38">
+      <c r="L15">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="M15" s="38">
+      <c r="M15">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="N15" s="38">
+      <c r="N15">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O15" s="38">
-        <v>0</v>
-      </c>
-      <c r="P15" s="38">
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
         <v>0.1</v>
       </c>
       <c r="Q15" s="3">
@@ -10813,59 +10812,59 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
-      <c r="B16" s="38">
-        <v>1</v>
-      </c>
-      <c r="C16" s="38">
-        <v>1</v>
-      </c>
-      <c r="D16" s="38">
-        <v>0</v>
-      </c>
-      <c r="E16" s="38">
-        <v>1</v>
-      </c>
-      <c r="F16" s="38">
+      <c r="A16" s="25"/>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="G16" s="38">
+      <c r="G16">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="I16" s="38">
+      <c r="I16">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="J16" s="38">
+      <c r="J16">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="K16" s="38">
+      <c r="K16">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L16" s="38">
+      <c r="L16">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="M16" s="38">
+      <c r="M16">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="N16" s="38">
+      <c r="N16">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O16" s="38">
-        <v>0</v>
-      </c>
-      <c r="P16" s="38">
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
         <v>0.1</v>
       </c>
       <c r="Q16" s="3">
@@ -10873,7 +10872,7 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="26"/>
       <c r="B17" s="4">
         <v>1</v>
       </c>
@@ -10999,7 +10998,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="21">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -11048,7 +11047,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
+      <c r="A3" s="19"/>
       <c r="B3">
         <v>0</v>
       </c>
@@ -11097,7 +11096,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
+      <c r="A4" s="19"/>
       <c r="B4">
         <v>1</v>
       </c>
@@ -11146,7 +11145,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
+      <c r="A5" s="20"/>
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -11195,7 +11194,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
+      <c r="A6" s="18">
         <v>2</v>
       </c>
       <c r="B6" s="1">
@@ -11246,7 +11245,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
+      <c r="A7" s="19"/>
       <c r="B7">
         <v>0</v>
       </c>
@@ -11295,7 +11294,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
+      <c r="A8" s="19"/>
       <c r="B8">
         <v>1</v>
       </c>
@@ -11344,7 +11343,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
+      <c r="A9" s="19"/>
       <c r="B9">
         <v>1</v>
       </c>
@@ -11393,7 +11392,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
+      <c r="A10" s="18">
         <v>3</v>
       </c>
       <c r="B10" s="1">
@@ -11444,7 +11443,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
+      <c r="A11" s="19"/>
       <c r="B11">
         <v>0</v>
       </c>
@@ -11493,7 +11492,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12">
         <v>1</v>
       </c>
@@ -11542,7 +11541,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
+      <c r="A13" s="19"/>
       <c r="B13">
         <v>1</v>
       </c>
@@ -11591,7 +11590,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="21">
+      <c r="A14" s="18">
         <v>4</v>
       </c>
       <c r="B14" s="1">
@@ -11642,7 +11641,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
+      <c r="A15" s="19"/>
       <c r="B15">
         <v>0</v>
       </c>
@@ -11691,7 +11690,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
+      <c r="A16" s="19"/>
       <c r="B16">
         <v>1</v>
       </c>
@@ -11740,7 +11739,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="23"/>
+      <c r="A17" s="20"/>
       <c r="B17" s="4">
         <v>1</v>
       </c>
@@ -11859,7 +11858,7 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="18">
+      <c r="A2" s="35">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -11918,7 +11917,7 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
+      <c r="A3" s="36"/>
       <c r="B3">
         <v>0</v>
       </c>
@@ -11978,7 +11977,7 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="19"/>
+      <c r="A4" s="36"/>
       <c r="B4">
         <v>0</v>
       </c>
@@ -12038,7 +12037,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
+      <c r="A5" s="36"/>
       <c r="B5">
         <v>0</v>
       </c>
@@ -12098,7 +12097,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="19"/>
+      <c r="A6" s="36"/>
       <c r="B6">
         <v>1</v>
       </c>
@@ -12158,7 +12157,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
+      <c r="A7" s="36"/>
       <c r="B7">
         <v>1</v>
       </c>
@@ -12218,7 +12217,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
+      <c r="A8" s="36"/>
       <c r="B8">
         <v>1</v>
       </c>
@@ -12278,59 +12277,59 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="38">
-        <v>1</v>
-      </c>
-      <c r="C9" s="38">
-        <v>1</v>
-      </c>
-      <c r="D9" s="38">
-        <v>1</v>
-      </c>
-      <c r="E9" s="38">
-        <v>1</v>
-      </c>
-      <c r="F9" s="38">
+      <c r="A9" s="36"/>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
         <f t="shared" si="6"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9">
         <f t="shared" si="6"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9">
         <f t="shared" si="6"/>
         <v>0.8</v>
       </c>
-      <c r="I9" s="38">
+      <c r="I9">
         <f t="shared" si="0"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="J9" s="38">
+      <c r="J9">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K9" s="38">
+      <c r="K9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L9" s="38">
+      <c r="L9">
         <f t="shared" si="3"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="M9" s="38">
+      <c r="M9">
         <f t="shared" si="4"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="N9" s="38">
+      <c r="N9">
         <f t="shared" si="5"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="O9" s="38">
-        <v>0</v>
-      </c>
-      <c r="P9" s="38">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
         <v>0.1</v>
       </c>
       <c r="Q9" s="3">
@@ -12338,7 +12337,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="35">
+      <c r="A10" s="24">
         <v>2</v>
       </c>
       <c r="B10" s="1">
@@ -12400,59 +12399,59 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="38">
-        <v>0</v>
-      </c>
-      <c r="C11" s="38">
-        <v>0</v>
-      </c>
-      <c r="D11" s="38">
+      <c r="A11" s="25"/>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F11">
         <f t="shared" si="6"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11">
         <f t="shared" si="6"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11">
         <f t="shared" si="6"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="I11" s="38">
+      <c r="I11">
         <f t="shared" ref="I11:I17" si="7">B11*F11+C11*G11+D11*H11+O11</f>
         <v>0.70000000000000007</v>
       </c>
-      <c r="J11" s="38">
+      <c r="J11">
         <f t="shared" ref="J11:J17" si="8">IF(I11&gt;Q11,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K11" s="38">
+      <c r="K11">
         <f t="shared" ref="K11:K17" si="9">E11-J11</f>
         <v>-1</v>
       </c>
-      <c r="L11" s="38">
+      <c r="L11">
         <f t="shared" ref="L11:L17" si="10">F11+(P11*K11*B11)</f>
         <v>0.70000000000000007</v>
       </c>
-      <c r="M11" s="38">
+      <c r="M11">
         <f t="shared" ref="M11:M17" si="11">F11+(P11*K11*C11)</f>
         <v>0.70000000000000007</v>
       </c>
-      <c r="N11" s="38">
+      <c r="N11">
         <f t="shared" ref="N11:N17" si="12">F11+(P11*K11*D11)</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="O11" s="38">
-        <v>0</v>
-      </c>
-      <c r="P11" s="38">
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
         <v>0.1</v>
       </c>
       <c r="Q11" s="3">
@@ -12460,59 +12459,59 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
-      <c r="B12" s="38">
-        <v>0</v>
-      </c>
-      <c r="C12" s="38">
-        <v>1</v>
-      </c>
-      <c r="D12" s="38">
+      <c r="A12" s="25"/>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="38">
+      <c r="F12">
         <f t="shared" si="6"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="G12" s="38">
+      <c r="G12">
         <f t="shared" si="6"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12">
         <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="I12" s="38">
+      <c r="I12">
         <f t="shared" si="7"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="J12" s="38">
+      <c r="J12">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K12" s="38">
+      <c r="K12">
         <f t="shared" si="9"/>
         <v>-1</v>
       </c>
-      <c r="L12" s="38">
+      <c r="L12">
         <f t="shared" si="10"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="M12" s="38">
+      <c r="M12">
         <f t="shared" si="11"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="N12" s="38">
+      <c r="N12">
         <f t="shared" si="12"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="O12" s="38">
-        <v>0</v>
-      </c>
-      <c r="P12" s="38">
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
         <v>0.1</v>
       </c>
       <c r="Q12" s="3">
@@ -12520,59 +12519,59 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="38">
-        <v>0</v>
-      </c>
-      <c r="C13" s="38">
-        <v>1</v>
-      </c>
-      <c r="D13" s="38">
+      <c r="A13" s="25"/>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="38">
+      <c r="F13">
         <f t="shared" si="6"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13">
         <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13">
         <f t="shared" si="6"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="I13" s="38">
+      <c r="I13">
         <f t="shared" si="7"/>
         <v>1.3000000000000003</v>
       </c>
-      <c r="J13" s="38">
+      <c r="J13">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K13" s="38">
+      <c r="K13">
         <f t="shared" si="9"/>
         <v>-1</v>
       </c>
-      <c r="L13" s="38">
+      <c r="L13">
         <f t="shared" si="10"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="M13" s="38">
+      <c r="M13">
         <f t="shared" si="11"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="N13" s="38">
+      <c r="N13">
         <f t="shared" si="12"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="O13" s="38">
-        <v>0</v>
-      </c>
-      <c r="P13" s="38">
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
         <v>0.1</v>
       </c>
       <c r="Q13" s="3">
@@ -12580,59 +12579,59 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
-      <c r="B14" s="38">
-        <v>1</v>
-      </c>
-      <c r="C14" s="38">
-        <v>0</v>
-      </c>
-      <c r="D14" s="38">
+      <c r="A14" s="25"/>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14">
         <f t="shared" si="6"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14">
         <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14">
         <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="I14" s="38">
+      <c r="I14">
         <f t="shared" si="7"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="J14" s="38">
+      <c r="J14">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K14" s="38">
+      <c r="K14">
         <f t="shared" si="9"/>
         <v>-1</v>
       </c>
-      <c r="L14" s="38">
+      <c r="L14">
         <f t="shared" si="10"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="M14" s="38">
+      <c r="M14">
         <f t="shared" si="11"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="N14" s="38">
+      <c r="N14">
         <f t="shared" si="12"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="O14" s="38">
-        <v>0</v>
-      </c>
-      <c r="P14" s="38">
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
         <v>0.1</v>
       </c>
       <c r="Q14" s="3">
@@ -12640,59 +12639,59 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="36"/>
-      <c r="B15" s="38">
-        <v>1</v>
-      </c>
-      <c r="C15" s="38">
-        <v>0</v>
-      </c>
-      <c r="D15" s="38">
+      <c r="A15" s="25"/>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15">
         <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="G15" s="38">
+      <c r="G15">
         <f t="shared" si="6"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="H15" s="38">
+      <c r="H15">
         <f t="shared" si="6"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="I15" s="38">
+      <c r="I15">
         <f t="shared" si="7"/>
         <v>1.3000000000000003</v>
       </c>
-      <c r="J15" s="38">
+      <c r="J15">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K15" s="38">
+      <c r="K15">
         <f t="shared" si="9"/>
         <v>-1</v>
       </c>
-      <c r="L15" s="38">
+      <c r="L15">
         <f t="shared" si="10"/>
         <v>0.50000000000000011</v>
       </c>
-      <c r="M15" s="38">
+      <c r="M15">
         <f t="shared" si="11"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="N15" s="38">
+      <c r="N15">
         <f t="shared" si="12"/>
         <v>0.50000000000000011</v>
       </c>
-      <c r="O15" s="38">
-        <v>0</v>
-      </c>
-      <c r="P15" s="38">
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
         <v>0.1</v>
       </c>
       <c r="Q15" s="3">
@@ -12700,59 +12699,59 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
-      <c r="B16" s="38">
-        <v>1</v>
-      </c>
-      <c r="C16" s="38">
-        <v>1</v>
-      </c>
-      <c r="D16" s="38">
+      <c r="A16" s="25"/>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16">
         <f t="shared" si="6"/>
         <v>0.50000000000000011</v>
       </c>
-      <c r="G16" s="38">
+      <c r="G16">
         <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16">
         <f t="shared" si="6"/>
         <v>0.50000000000000011</v>
       </c>
-      <c r="I16" s="38">
+      <c r="I16">
         <f t="shared" si="7"/>
         <v>1.1000000000000001</v>
       </c>
-      <c r="J16" s="38">
+      <c r="J16">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K16" s="38">
+      <c r="K16">
         <f t="shared" si="9"/>
         <v>-1</v>
       </c>
-      <c r="L16" s="38">
+      <c r="L16">
         <f t="shared" si="10"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="M16" s="38">
+      <c r="M16">
         <f t="shared" si="11"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="N16" s="38">
+      <c r="N16">
         <f t="shared" si="12"/>
         <v>0.50000000000000011</v>
       </c>
-      <c r="O16" s="38">
-        <v>0</v>
-      </c>
-      <c r="P16" s="38">
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
         <v>0.1</v>
       </c>
       <c r="Q16" s="3">
@@ -12760,7 +12759,7 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="26"/>
       <c r="B17" s="4">
         <v>1</v>
       </c>
@@ -12820,7 +12819,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="35">
+      <c r="A18" s="24">
         <v>3</v>
       </c>
       <c r="B18" s="1">
@@ -12882,59 +12881,59 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
-      <c r="B19" s="38">
-        <v>0</v>
-      </c>
-      <c r="C19" s="38">
-        <v>0</v>
-      </c>
-      <c r="D19" s="38">
+      <c r="A19" s="25"/>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
         <v>1</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F19">
         <f t="shared" si="13"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="G19" s="38">
+      <c r="G19">
         <f t="shared" si="14"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="H19" s="38">
+      <c r="H19">
         <f t="shared" si="15"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="I19" s="38">
+      <c r="I19">
         <f t="shared" ref="I19:I25" si="16">B19*F19+C19*G19+D19*H19+O19</f>
         <v>0.40000000000000013</v>
       </c>
-      <c r="J19" s="38">
+      <c r="J19">
         <f t="shared" ref="J19:J25" si="17">IF(I19&gt;Q19,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K19" s="38">
+      <c r="K19">
         <f t="shared" ref="K19:K25" si="18">E19-J19</f>
         <v>0</v>
       </c>
-      <c r="L19" s="38">
+      <c r="L19">
         <f t="shared" ref="L19:L25" si="19">F19+(P19*K19*B19)</f>
         <v>0.40000000000000013</v>
       </c>
-      <c r="M19" s="38">
+      <c r="M19">
         <f t="shared" ref="M19:M25" si="20">F19+(P19*K19*C19)</f>
         <v>0.40000000000000013</v>
       </c>
-      <c r="N19" s="38">
+      <c r="N19">
         <f t="shared" ref="N19:N25" si="21">F19+(P19*K19*D19)</f>
         <v>0.40000000000000013</v>
       </c>
-      <c r="O19" s="38">
-        <v>0</v>
-      </c>
-      <c r="P19" s="38">
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
         <v>0.1</v>
       </c>
       <c r="Q19" s="3">
@@ -12942,59 +12941,59 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="36"/>
-      <c r="B20" s="38">
-        <v>0</v>
-      </c>
-      <c r="C20" s="38">
-        <v>1</v>
-      </c>
-      <c r="D20" s="38">
+      <c r="A20" s="25"/>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20" s="38">
+      <c r="F20">
         <f t="shared" si="13"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="G20" s="38">
+      <c r="G20">
         <f t="shared" si="14"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="H20" s="38">
+      <c r="H20">
         <f t="shared" si="15"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="I20" s="38">
+      <c r="I20">
         <f t="shared" si="16"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="J20" s="38">
+      <c r="J20">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K20" s="38">
+      <c r="K20">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L20" s="38">
+      <c r="L20">
         <f t="shared" si="19"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="M20" s="38">
+      <c r="M20">
         <f t="shared" si="20"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="N20" s="38">
+      <c r="N20">
         <f t="shared" si="21"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="O20" s="38">
-        <v>0</v>
-      </c>
-      <c r="P20" s="38">
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
         <v>0.1</v>
       </c>
       <c r="Q20" s="3">
@@ -13002,59 +13001,59 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="38">
-        <v>0</v>
-      </c>
-      <c r="C21" s="38">
-        <v>1</v>
-      </c>
-      <c r="D21" s="38">
+      <c r="A21" s="25"/>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
-      <c r="F21" s="38">
+      <c r="F21">
         <f t="shared" si="13"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="G21" s="38">
+      <c r="G21">
         <f t="shared" si="14"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="H21" s="38">
+      <c r="H21">
         <f t="shared" si="15"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="I21" s="38">
+      <c r="I21">
         <f t="shared" si="16"/>
         <v>0.80000000000000027</v>
       </c>
-      <c r="J21" s="38">
+      <c r="J21">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="K21" s="38">
+      <c r="K21">
         <f t="shared" si="18"/>
         <v>-1</v>
       </c>
-      <c r="L21" s="38">
+      <c r="L21">
         <f t="shared" si="19"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="M21" s="38">
+      <c r="M21">
         <f t="shared" si="20"/>
         <v>0.30000000000000016</v>
       </c>
-      <c r="N21" s="38">
+      <c r="N21">
         <f t="shared" si="21"/>
         <v>0.30000000000000016</v>
       </c>
-      <c r="O21" s="38">
-        <v>0</v>
-      </c>
-      <c r="P21" s="38">
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
         <v>0.1</v>
       </c>
       <c r="Q21" s="3">
@@ -13062,59 +13061,59 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="36"/>
-      <c r="B22" s="38">
-        <v>1</v>
-      </c>
-      <c r="C22" s="38">
-        <v>0</v>
-      </c>
-      <c r="D22" s="38">
+      <c r="A22" s="25"/>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22">
         <f t="shared" si="13"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="G22" s="38">
+      <c r="G22">
         <f t="shared" si="14"/>
         <v>0.30000000000000016</v>
       </c>
-      <c r="H22" s="38">
+      <c r="H22">
         <f t="shared" si="15"/>
         <v>0.30000000000000016</v>
       </c>
-      <c r="I22" s="38">
+      <c r="I22">
         <f t="shared" si="16"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="J22" s="38">
+      <c r="J22">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K22" s="38">
+      <c r="K22">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L22" s="38">
+      <c r="L22">
         <f t="shared" si="19"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="M22" s="38">
+      <c r="M22">
         <f t="shared" si="20"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="N22" s="38">
+      <c r="N22">
         <f t="shared" si="21"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="O22" s="38">
-        <v>0</v>
-      </c>
-      <c r="P22" s="38">
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
         <v>0.1</v>
       </c>
       <c r="Q22" s="3">
@@ -13122,59 +13121,59 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="36"/>
-      <c r="B23" s="38">
-        <v>1</v>
-      </c>
-      <c r="C23" s="38">
-        <v>0</v>
-      </c>
-      <c r="D23" s="38">
+      <c r="A23" s="25"/>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
-      <c r="F23" s="38">
+      <c r="F23">
         <f t="shared" si="13"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="G23" s="38">
+      <c r="G23">
         <f t="shared" si="14"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="H23" s="38">
+      <c r="H23">
         <f t="shared" si="15"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="I23" s="38">
+      <c r="I23">
         <f t="shared" si="16"/>
         <v>0.80000000000000027</v>
       </c>
-      <c r="J23" s="38">
+      <c r="J23">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="K23" s="38">
+      <c r="K23">
         <f t="shared" si="18"/>
         <v>-1</v>
       </c>
-      <c r="L23" s="38">
+      <c r="L23">
         <f t="shared" si="19"/>
         <v>0.30000000000000016</v>
       </c>
-      <c r="M23" s="38">
+      <c r="M23">
         <f t="shared" si="20"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="N23" s="38">
+      <c r="N23">
         <f t="shared" si="21"/>
         <v>0.30000000000000016</v>
       </c>
-      <c r="O23" s="38">
-        <v>0</v>
-      </c>
-      <c r="P23" s="38">
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
         <v>0.1</v>
       </c>
       <c r="Q23" s="3">
@@ -13182,59 +13181,59 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="36"/>
-      <c r="B24" s="38">
-        <v>1</v>
-      </c>
-      <c r="C24" s="38">
-        <v>1</v>
-      </c>
-      <c r="D24" s="38">
+      <c r="A24" s="25"/>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
-      <c r="F24" s="38">
+      <c r="F24">
         <f t="shared" si="13"/>
         <v>0.30000000000000016</v>
       </c>
-      <c r="G24" s="38">
+      <c r="G24">
         <f t="shared" si="14"/>
         <v>0.40000000000000013</v>
       </c>
-      <c r="H24" s="38">
+      <c r="H24">
         <f t="shared" si="15"/>
         <v>0.30000000000000016</v>
       </c>
-      <c r="I24" s="38">
+      <c r="I24">
         <f t="shared" si="16"/>
         <v>0.70000000000000029</v>
       </c>
-      <c r="J24" s="38">
+      <c r="J24">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="K24" s="38">
+      <c r="K24">
         <f t="shared" si="18"/>
         <v>-1</v>
       </c>
-      <c r="L24" s="38">
+      <c r="L24">
         <f t="shared" si="19"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="M24" s="38">
+      <c r="M24">
         <f t="shared" si="20"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="N24" s="38">
+      <c r="N24">
         <f t="shared" si="21"/>
         <v>0.30000000000000016</v>
       </c>
-      <c r="O24" s="38">
-        <v>0</v>
-      </c>
-      <c r="P24" s="38">
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
         <v>0.1</v>
       </c>
       <c r="Q24" s="3">
@@ -13242,7 +13241,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+      <c r="A25" s="26"/>
       <c r="B25" s="4">
         <v>1</v>
       </c>
@@ -13302,7 +13301,7 @@
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="35">
+      <c r="A26" s="24">
         <v>4</v>
       </c>
       <c r="B26" s="1">
@@ -13364,59 +13363,59 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="36"/>
-      <c r="B27" s="38">
-        <v>0</v>
-      </c>
-      <c r="C27" s="38">
-        <v>0</v>
-      </c>
-      <c r="D27" s="38">
+      <c r="A27" s="25"/>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
-      <c r="F27" s="38">
+      <c r="F27">
         <f t="shared" si="22"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="G27" s="38">
+      <c r="G27">
         <f t="shared" si="23"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="H27" s="38">
+      <c r="H27">
         <f t="shared" si="24"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="I27" s="38">
+      <c r="I27">
         <f t="shared" ref="I27:I33" si="25">B27*F27+C27*G27+D27*H27+O27</f>
         <v>0.20000000000000015</v>
       </c>
-      <c r="J27" s="38">
+      <c r="J27">
         <f t="shared" ref="J27:J33" si="26">IF(I27&gt;Q27,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K27" s="38">
+      <c r="K27">
         <f t="shared" ref="K27:K33" si="27">E27-J27</f>
         <v>0</v>
       </c>
-      <c r="L27" s="38">
+      <c r="L27">
         <f t="shared" ref="L27:L33" si="28">F27+(P27*K27*B27)</f>
         <v>0.20000000000000015</v>
       </c>
-      <c r="M27" s="38">
+      <c r="M27">
         <f t="shared" ref="M27:M33" si="29">F27+(P27*K27*C27)</f>
         <v>0.20000000000000015</v>
       </c>
-      <c r="N27" s="38">
+      <c r="N27">
         <f t="shared" ref="N27:N33" si="30">F27+(P27*K27*D27)</f>
         <v>0.20000000000000015</v>
       </c>
-      <c r="O27" s="38">
-        <v>0</v>
-      </c>
-      <c r="P27" s="38">
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
         <v>0.1</v>
       </c>
       <c r="Q27" s="3">
@@ -13424,59 +13423,59 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="36"/>
-      <c r="B28" s="38">
-        <v>0</v>
-      </c>
-      <c r="C28" s="38">
-        <v>1</v>
-      </c>
-      <c r="D28" s="38">
+      <c r="A28" s="25"/>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28" s="38">
+      <c r="F28">
         <f t="shared" si="22"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="G28" s="38">
+      <c r="G28">
         <f t="shared" si="23"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="H28" s="38">
+      <c r="H28">
         <f t="shared" si="24"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="I28" s="38">
+      <c r="I28">
         <f t="shared" si="25"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="J28" s="38">
+      <c r="J28">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="K28" s="38">
+      <c r="K28">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="L28" s="38">
+      <c r="L28">
         <f t="shared" si="28"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="M28" s="38">
+      <c r="M28">
         <f t="shared" si="29"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="N28" s="38">
+      <c r="N28">
         <f t="shared" si="30"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="O28" s="38">
-        <v>0</v>
-      </c>
-      <c r="P28" s="38">
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
         <v>0.1</v>
       </c>
       <c r="Q28" s="3">
@@ -13484,59 +13483,59 @@
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="36"/>
-      <c r="B29" s="38">
-        <v>0</v>
-      </c>
-      <c r="C29" s="38">
-        <v>1</v>
-      </c>
-      <c r="D29" s="38">
+      <c r="A29" s="25"/>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
         <v>1</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
-      <c r="F29" s="38">
+      <c r="F29">
         <f t="shared" si="22"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="G29" s="38">
+      <c r="G29">
         <f t="shared" si="23"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="H29" s="38">
+      <c r="H29">
         <f t="shared" si="24"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="I29" s="38">
+      <c r="I29">
         <f t="shared" si="25"/>
         <v>0.4000000000000003</v>
       </c>
-      <c r="J29" s="38">
+      <c r="J29">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="K29" s="38">
+      <c r="K29">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="L29" s="38">
+      <c r="L29">
         <f t="shared" si="28"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="M29" s="38">
+      <c r="M29">
         <f t="shared" si="29"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="N29" s="38">
+      <c r="N29">
         <f t="shared" si="30"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="O29" s="38">
-        <v>0</v>
-      </c>
-      <c r="P29" s="38">
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
         <v>0.1</v>
       </c>
       <c r="Q29" s="3">
@@ -13544,59 +13543,59 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="38">
-        <v>1</v>
-      </c>
-      <c r="C30" s="38">
-        <v>0</v>
-      </c>
-      <c r="D30" s="38">
+      <c r="A30" s="25"/>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
-      <c r="F30" s="38">
+      <c r="F30">
         <f t="shared" si="22"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="G30" s="38">
+      <c r="G30">
         <f t="shared" si="23"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="H30" s="38">
+      <c r="H30">
         <f t="shared" si="24"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="I30" s="38">
+      <c r="I30">
         <f t="shared" si="25"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="J30" s="38">
+      <c r="J30">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="K30" s="38">
+      <c r="K30">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="L30" s="38">
+      <c r="L30">
         <f t="shared" si="28"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="M30" s="38">
+      <c r="M30">
         <f t="shared" si="29"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="N30" s="38">
+      <c r="N30">
         <f t="shared" si="30"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="O30" s="38">
-        <v>0</v>
-      </c>
-      <c r="P30" s="38">
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
         <v>0.1</v>
       </c>
       <c r="Q30" s="3">
@@ -13604,59 +13603,59 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="36"/>
-      <c r="B31" s="38">
-        <v>1</v>
-      </c>
-      <c r="C31" s="38">
-        <v>0</v>
-      </c>
-      <c r="D31" s="38">
+      <c r="A31" s="25"/>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
-      <c r="F31" s="38">
+      <c r="F31">
         <f t="shared" si="22"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="G31" s="38">
+      <c r="G31">
         <f t="shared" si="23"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="H31" s="38">
+      <c r="H31">
         <f t="shared" si="24"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="I31" s="38">
+      <c r="I31">
         <f t="shared" si="25"/>
         <v>0.4000000000000003</v>
       </c>
-      <c r="J31" s="38">
+      <c r="J31">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="K31" s="38">
+      <c r="K31">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="L31" s="38">
+      <c r="L31">
         <f t="shared" si="28"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="M31" s="38">
+      <c r="M31">
         <f t="shared" si="29"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="N31" s="38">
+      <c r="N31">
         <f t="shared" si="30"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="O31" s="38">
-        <v>0</v>
-      </c>
-      <c r="P31" s="38">
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
         <v>0.1</v>
       </c>
       <c r="Q31" s="3">
@@ -13664,59 +13663,59 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="36"/>
-      <c r="B32" s="38">
-        <v>1</v>
-      </c>
-      <c r="C32" s="38">
-        <v>1</v>
-      </c>
-      <c r="D32" s="38">
+      <c r="A32" s="25"/>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
-      <c r="F32" s="38">
+      <c r="F32">
         <f t="shared" si="22"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="G32" s="38">
+      <c r="G32">
         <f t="shared" si="23"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="H32" s="38">
+      <c r="H32">
         <f t="shared" si="24"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="I32" s="38">
+      <c r="I32">
         <f t="shared" si="25"/>
         <v>0.4000000000000003</v>
       </c>
-      <c r="J32" s="38">
+      <c r="J32">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="K32" s="38">
+      <c r="K32">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="L32" s="38">
+      <c r="L32">
         <f t="shared" si="28"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="M32" s="38">
+      <c r="M32">
         <f t="shared" si="29"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="N32" s="38">
+      <c r="N32">
         <f t="shared" si="30"/>
         <v>0.20000000000000015</v>
       </c>
-      <c r="O32" s="38">
-        <v>0</v>
-      </c>
-      <c r="P32" s="38">
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
         <v>0.1</v>
       </c>
       <c r="Q32" s="3">
@@ -13724,7 +13723,7 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+      <c r="A33" s="26"/>
       <c r="B33" s="4">
         <v>1</v>
       </c>
@@ -13844,7 +13843,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="21">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -13893,7 +13892,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
+      <c r="A3" s="19"/>
       <c r="B3">
         <v>0</v>
       </c>
@@ -13942,7 +13941,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
+      <c r="A4" s="19"/>
       <c r="B4">
         <v>1</v>
       </c>
@@ -13991,7 +13990,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
+      <c r="A5" s="20"/>
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -14040,7 +14039,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
+      <c r="A6" s="18">
         <v>2</v>
       </c>
       <c r="B6" s="1">
@@ -14091,7 +14090,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
+      <c r="A7" s="19"/>
       <c r="B7">
         <v>0</v>
       </c>
@@ -14140,7 +14139,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
+      <c r="A8" s="19"/>
       <c r="B8">
         <v>1</v>
       </c>
@@ -14189,7 +14188,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
+      <c r="A9" s="20"/>
       <c r="B9" s="4">
         <v>1</v>
       </c>
@@ -14238,7 +14237,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
+      <c r="A10" s="18">
         <v>3</v>
       </c>
       <c r="B10" s="1">
@@ -14289,7 +14288,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
+      <c r="A11" s="19"/>
       <c r="B11">
         <v>0</v>
       </c>
@@ -14338,7 +14337,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12">
         <v>1</v>
       </c>
@@ -14387,7 +14386,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="23"/>
+      <c r="A13" s="20"/>
       <c r="B13" s="4">
         <v>1</v>
       </c>
@@ -14436,7 +14435,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="21">
+      <c r="A14" s="18">
         <v>4</v>
       </c>
       <c r="B14" s="1">
@@ -14487,7 +14486,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
+      <c r="A15" s="19"/>
       <c r="B15">
         <v>0</v>
       </c>
@@ -14536,7 +14535,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
+      <c r="A16" s="19"/>
       <c r="B16">
         <v>1</v>
       </c>
@@ -14585,7 +14584,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="23"/>
+      <c r="A17" s="20"/>
       <c r="B17" s="4">
         <v>1</v>
       </c>
@@ -14634,7 +14633,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="21">
+      <c r="A18" s="18">
         <v>5</v>
       </c>
       <c r="B18" s="1">
@@ -14685,7 +14684,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="22"/>
+      <c r="A19" s="19"/>
       <c r="B19">
         <v>0</v>
       </c>
@@ -14734,7 +14733,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="22"/>
+      <c r="A20" s="19"/>
       <c r="B20">
         <v>1</v>
       </c>
@@ -14783,7 +14782,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="23"/>
+      <c r="A21" s="20"/>
       <c r="B21" s="4">
         <v>1</v>
       </c>
@@ -14902,7 +14901,7 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="18">
+      <c r="A2" s="35">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -14950,7 +14949,7 @@
         <f>F2+(P2*K2*D2)</f>
         <v>0.1</v>
       </c>
-      <c r="O2" s="38">
+      <c r="O2">
         <v>1</v>
       </c>
       <c r="P2" s="1">
@@ -14961,7 +14960,7 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
+      <c r="A3" s="36"/>
       <c r="B3">
         <v>0</v>
       </c>
@@ -15010,7 +15009,7 @@
         <f t="shared" ref="N3:N9" si="5">F3+(P3*K3*D3)</f>
         <v>0.1</v>
       </c>
-      <c r="O3" s="38">
+      <c r="O3">
         <v>1</v>
       </c>
       <c r="P3">
@@ -15021,7 +15020,7 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="19"/>
+      <c r="A4" s="36"/>
       <c r="B4">
         <v>0</v>
       </c>
@@ -15070,7 +15069,7 @@
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4">
         <v>1</v>
       </c>
       <c r="P4">
@@ -15081,7 +15080,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
+      <c r="A5" s="36"/>
       <c r="B5">
         <v>0</v>
       </c>
@@ -15130,7 +15129,7 @@
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
-      <c r="O5" s="38">
+      <c r="O5">
         <v>1</v>
       </c>
       <c r="P5">
@@ -15141,7 +15140,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="19"/>
+      <c r="A6" s="36"/>
       <c r="B6">
         <v>1</v>
       </c>
@@ -15190,7 +15189,7 @@
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
-      <c r="O6" s="38">
+      <c r="O6">
         <v>1</v>
       </c>
       <c r="P6">
@@ -15201,7 +15200,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
+      <c r="A7" s="36"/>
       <c r="B7">
         <v>1</v>
       </c>
@@ -15250,7 +15249,7 @@
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
-      <c r="O7" s="38">
+      <c r="O7">
         <v>1</v>
       </c>
       <c r="P7">
@@ -15261,7 +15260,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
+      <c r="A8" s="36"/>
       <c r="B8">
         <v>1</v>
       </c>
@@ -15310,7 +15309,7 @@
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
-      <c r="O8" s="38">
+      <c r="O8">
         <v>1</v>
       </c>
       <c r="P8">
@@ -15321,59 +15320,59 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="38">
-        <v>1</v>
-      </c>
-      <c r="C9" s="38">
-        <v>1</v>
-      </c>
-      <c r="D9" s="38">
-        <v>1</v>
-      </c>
-      <c r="E9" s="38">
-        <v>0</v>
-      </c>
-      <c r="F9" s="38">
+      <c r="A9" s="36"/>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <f t="shared" si="6"/>
         <v>0.1</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9">
         <f t="shared" si="6"/>
         <v>0.1</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9">
         <f t="shared" si="6"/>
         <v>0.1</v>
       </c>
-      <c r="I9" s="38">
+      <c r="I9">
         <f t="shared" si="0"/>
         <v>1.3</v>
       </c>
-      <c r="J9" s="38">
+      <c r="J9">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K9" s="38">
+      <c r="K9">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
-      <c r="L9" s="38">
+      <c r="L9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M9" s="38">
+      <c r="M9">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N9" s="38">
+      <c r="N9">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O9" s="4">
         <v>1</v>
       </c>
-      <c r="P9" s="38">
+      <c r="P9">
         <v>0.1</v>
       </c>
       <c r="Q9" s="3">
@@ -15381,7 +15380,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="35">
+      <c r="A10" s="24">
         <v>2</v>
       </c>
       <c r="B10" s="1">
@@ -15432,7 +15431,7 @@
         <f>F10+(P10*K10*D10)</f>
         <v>0</v>
       </c>
-      <c r="O10" s="38">
+      <c r="O10">
         <v>1</v>
       </c>
       <c r="P10" s="1">
@@ -15443,59 +15442,59 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="38">
-        <v>0</v>
-      </c>
-      <c r="C11" s="38">
-        <v>0</v>
-      </c>
-      <c r="D11" s="38">
-        <v>1</v>
-      </c>
-      <c r="E11" s="38">
-        <v>1</v>
-      </c>
-      <c r="F11" s="38">
+      <c r="A11" s="25"/>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I11" s="38">
+      <c r="I11">
         <f t="shared" ref="I11:I17" si="7">B11*F11+C11*G11+D11*H11+O11</f>
         <v>1</v>
       </c>
-      <c r="J11" s="38">
+      <c r="J11">
         <f t="shared" ref="J11:J17" si="8">IF(I11&gt;Q11,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K11" s="38">
+      <c r="K11">
         <f t="shared" ref="K11:K17" si="9">E11-J11</f>
         <v>0</v>
       </c>
-      <c r="L11" s="38">
+      <c r="L11">
         <f t="shared" ref="L11:L17" si="10">F11+(P11*K11*B11)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="38">
+      <c r="M11">
         <f t="shared" ref="M11:M17" si="11">F11+(P11*K11*C11)</f>
         <v>0</v>
       </c>
-      <c r="N11" s="38">
+      <c r="N11">
         <f t="shared" ref="N11:N17" si="12">F11+(P11*K11*D11)</f>
         <v>0</v>
       </c>
-      <c r="O11" s="38">
-        <v>1</v>
-      </c>
-      <c r="P11" s="38">
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
         <v>0.1</v>
       </c>
       <c r="Q11" s="3">
@@ -15503,59 +15502,59 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
-      <c r="B12" s="38">
-        <v>0</v>
-      </c>
-      <c r="C12" s="38">
-        <v>1</v>
-      </c>
-      <c r="D12" s="38">
-        <v>0</v>
-      </c>
-      <c r="E12" s="38">
-        <v>1</v>
-      </c>
-      <c r="F12" s="38">
+      <c r="A12" s="25"/>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G12" s="38">
+      <c r="G12">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I12" s="38">
+      <c r="I12">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J12" s="38">
+      <c r="J12">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K12" s="38">
+      <c r="K12">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L12" s="38">
+      <c r="L12">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M12" s="38">
+      <c r="M12">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="N12" s="38">
+      <c r="N12">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="O12" s="38">
-        <v>1</v>
-      </c>
-      <c r="P12" s="38">
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
         <v>0.1</v>
       </c>
       <c r="Q12" s="3">
@@ -15563,59 +15562,59 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="38">
-        <v>0</v>
-      </c>
-      <c r="C13" s="38">
-        <v>1</v>
-      </c>
-      <c r="D13" s="38">
-        <v>1</v>
-      </c>
-      <c r="E13" s="38">
-        <v>1</v>
-      </c>
-      <c r="F13" s="38">
+      <c r="A13" s="25"/>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I13" s="38">
+      <c r="I13">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J13" s="38">
+      <c r="J13">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K13" s="38">
+      <c r="K13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L13" s="38">
+      <c r="L13">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M13" s="38">
+      <c r="M13">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="N13" s="38">
+      <c r="N13">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="O13" s="38">
-        <v>1</v>
-      </c>
-      <c r="P13" s="38">
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
         <v>0.1</v>
       </c>
       <c r="Q13" s="3">
@@ -15623,59 +15622,59 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
-      <c r="B14" s="38">
-        <v>1</v>
-      </c>
-      <c r="C14" s="38">
-        <v>0</v>
-      </c>
-      <c r="D14" s="38">
-        <v>0</v>
-      </c>
-      <c r="E14" s="38">
-        <v>1</v>
-      </c>
-      <c r="F14" s="38">
+      <c r="A14" s="25"/>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I14" s="38">
+      <c r="I14">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J14" s="38">
+      <c r="J14">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K14" s="38">
+      <c r="K14">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L14" s="38">
+      <c r="L14">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M14" s="38">
+      <c r="M14">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="N14" s="38">
+      <c r="N14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="O14" s="38">
-        <v>1</v>
-      </c>
-      <c r="P14" s="38">
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
         <v>0.1</v>
       </c>
       <c r="Q14" s="3">
@@ -15683,59 +15682,59 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="36"/>
-      <c r="B15" s="38">
-        <v>1</v>
-      </c>
-      <c r="C15" s="38">
-        <v>0</v>
-      </c>
-      <c r="D15" s="38">
-        <v>1</v>
-      </c>
-      <c r="E15" s="38">
-        <v>1</v>
-      </c>
-      <c r="F15" s="38">
+      <c r="A15" s="25"/>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G15" s="38">
+      <c r="G15">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H15" s="38">
+      <c r="H15">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I15" s="38">
+      <c r="I15">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J15" s="38">
+      <c r="J15">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K15" s="38">
+      <c r="K15">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L15" s="38">
+      <c r="L15">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M15" s="38">
+      <c r="M15">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="N15" s="38">
+      <c r="N15">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="O15" s="38">
-        <v>1</v>
-      </c>
-      <c r="P15" s="38">
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
         <v>0.1</v>
       </c>
       <c r="Q15" s="3">
@@ -15743,59 +15742,59 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
-      <c r="B16" s="38">
-        <v>1</v>
-      </c>
-      <c r="C16" s="38">
-        <v>1</v>
-      </c>
-      <c r="D16" s="38">
-        <v>0</v>
-      </c>
-      <c r="E16" s="38">
-        <v>1</v>
-      </c>
-      <c r="F16" s="38">
+      <c r="A16" s="25"/>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G16" s="38">
+      <c r="G16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I16" s="38">
+      <c r="I16">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J16" s="38">
+      <c r="J16">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K16" s="38">
+      <c r="K16">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L16" s="38">
+      <c r="L16">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M16" s="38">
+      <c r="M16">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="N16" s="38">
+      <c r="N16">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="O16" s="38">
-        <v>1</v>
-      </c>
-      <c r="P16" s="38">
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
         <v>0.1</v>
       </c>
       <c r="Q16" s="3">
@@ -15803,7 +15802,7 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="26"/>
       <c r="B17" s="4">
         <v>1</v>
       </c>
@@ -15863,7 +15862,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="35">
+      <c r="A18" s="24">
         <v>3</v>
       </c>
       <c r="B18" s="1">
@@ -15914,7 +15913,7 @@
         <f>F18+(P18*K18*D18)</f>
         <v>-0.1</v>
       </c>
-      <c r="O18" s="38">
+      <c r="O18">
         <v>1</v>
       </c>
       <c r="P18" s="1">
@@ -15925,59 +15924,59 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
-      <c r="B19" s="38">
-        <v>0</v>
-      </c>
-      <c r="C19" s="38">
-        <v>0</v>
-      </c>
-      <c r="D19" s="38">
-        <v>1</v>
-      </c>
-      <c r="E19" s="38">
-        <v>1</v>
-      </c>
-      <c r="F19" s="38">
+      <c r="A19" s="25"/>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
         <f t="shared" si="13"/>
         <v>-0.1</v>
       </c>
-      <c r="G19" s="38">
+      <c r="G19">
         <f t="shared" si="14"/>
         <v>-0.1</v>
       </c>
-      <c r="H19" s="38">
+      <c r="H19">
         <f t="shared" si="15"/>
         <v>-0.1</v>
       </c>
-      <c r="I19" s="38">
+      <c r="I19">
         <f t="shared" ref="I19:I25" si="16">B19*F19+C19*G19+D19*H19+O19</f>
         <v>0.9</v>
       </c>
-      <c r="J19" s="38">
+      <c r="J19">
         <f t="shared" ref="J19:J25" si="17">IF(I19&gt;Q19,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K19" s="38">
+      <c r="K19">
         <f t="shared" ref="K19:K25" si="18">E19-J19</f>
         <v>0</v>
       </c>
-      <c r="L19" s="38">
+      <c r="L19">
         <f t="shared" ref="L19:L25" si="19">F19+(P19*K19*B19)</f>
         <v>-0.1</v>
       </c>
-      <c r="M19" s="38">
+      <c r="M19">
         <f t="shared" ref="M19:M25" si="20">F19+(P19*K19*C19)</f>
         <v>-0.1</v>
       </c>
-      <c r="N19" s="38">
+      <c r="N19">
         <f t="shared" ref="N19:N25" si="21">F19+(P19*K19*D19)</f>
         <v>-0.1</v>
       </c>
-      <c r="O19" s="38">
-        <v>1</v>
-      </c>
-      <c r="P19" s="38">
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
         <v>0.1</v>
       </c>
       <c r="Q19" s="3">
@@ -15985,59 +15984,59 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="36"/>
-      <c r="B20" s="38">
-        <v>0</v>
-      </c>
-      <c r="C20" s="38">
-        <v>1</v>
-      </c>
-      <c r="D20" s="38">
-        <v>0</v>
-      </c>
-      <c r="E20" s="38">
-        <v>1</v>
-      </c>
-      <c r="F20" s="38">
+      <c r="A20" s="25"/>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
         <f t="shared" si="13"/>
         <v>-0.1</v>
       </c>
-      <c r="G20" s="38">
+      <c r="G20">
         <f t="shared" si="14"/>
         <v>-0.1</v>
       </c>
-      <c r="H20" s="38">
+      <c r="H20">
         <f t="shared" si="15"/>
         <v>-0.1</v>
       </c>
-      <c r="I20" s="38">
+      <c r="I20">
         <f t="shared" si="16"/>
         <v>0.9</v>
       </c>
-      <c r="J20" s="38">
+      <c r="J20">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="K20" s="38">
+      <c r="K20">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L20" s="38">
+      <c r="L20">
         <f t="shared" si="19"/>
         <v>-0.1</v>
       </c>
-      <c r="M20" s="38">
+      <c r="M20">
         <f t="shared" si="20"/>
         <v>-0.1</v>
       </c>
-      <c r="N20" s="38">
+      <c r="N20">
         <f t="shared" si="21"/>
         <v>-0.1</v>
       </c>
-      <c r="O20" s="38">
-        <v>1</v>
-      </c>
-      <c r="P20" s="38">
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
         <v>0.1</v>
       </c>
       <c r="Q20" s="3">
@@ -16045,59 +16044,59 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="38">
-        <v>0</v>
-      </c>
-      <c r="C21" s="38">
-        <v>1</v>
-      </c>
-      <c r="D21" s="38">
-        <v>1</v>
-      </c>
-      <c r="E21" s="38">
-        <v>1</v>
-      </c>
-      <c r="F21" s="38">
+      <c r="A21" s="25"/>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
         <f t="shared" si="13"/>
         <v>-0.1</v>
       </c>
-      <c r="G21" s="38">
+      <c r="G21">
         <f t="shared" si="14"/>
         <v>-0.1</v>
       </c>
-      <c r="H21" s="38">
+      <c r="H21">
         <f t="shared" si="15"/>
         <v>-0.1</v>
       </c>
-      <c r="I21" s="38">
+      <c r="I21">
         <f t="shared" si="16"/>
         <v>0.8</v>
       </c>
-      <c r="J21" s="38">
+      <c r="J21">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="K21" s="38">
+      <c r="K21">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L21" s="38">
+      <c r="L21">
         <f t="shared" si="19"/>
         <v>-0.1</v>
       </c>
-      <c r="M21" s="38">
+      <c r="M21">
         <f t="shared" si="20"/>
         <v>-0.1</v>
       </c>
-      <c r="N21" s="38">
+      <c r="N21">
         <f t="shared" si="21"/>
         <v>-0.1</v>
       </c>
-      <c r="O21" s="38">
-        <v>1</v>
-      </c>
-      <c r="P21" s="38">
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
         <v>0.1</v>
       </c>
       <c r="Q21" s="3">
@@ -16105,59 +16104,59 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="36"/>
-      <c r="B22" s="38">
-        <v>1</v>
-      </c>
-      <c r="C22" s="38">
-        <v>0</v>
-      </c>
-      <c r="D22" s="38">
-        <v>0</v>
-      </c>
-      <c r="E22" s="38">
-        <v>1</v>
-      </c>
-      <c r="F22" s="38">
+      <c r="A22" s="25"/>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
         <f t="shared" si="13"/>
         <v>-0.1</v>
       </c>
-      <c r="G22" s="38">
+      <c r="G22">
         <f t="shared" si="14"/>
         <v>-0.1</v>
       </c>
-      <c r="H22" s="38">
+      <c r="H22">
         <f t="shared" si="15"/>
         <v>-0.1</v>
       </c>
-      <c r="I22" s="38">
+      <c r="I22">
         <f t="shared" si="16"/>
         <v>0.9</v>
       </c>
-      <c r="J22" s="38">
+      <c r="J22">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="K22" s="38">
+      <c r="K22">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L22" s="38">
+      <c r="L22">
         <f t="shared" si="19"/>
         <v>-0.1</v>
       </c>
-      <c r="M22" s="38">
+      <c r="M22">
         <f t="shared" si="20"/>
         <v>-0.1</v>
       </c>
-      <c r="N22" s="38">
+      <c r="N22">
         <f t="shared" si="21"/>
         <v>-0.1</v>
       </c>
-      <c r="O22" s="38">
-        <v>1</v>
-      </c>
-      <c r="P22" s="38">
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
         <v>0.1</v>
       </c>
       <c r="Q22" s="3">
@@ -16165,59 +16164,59 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="36"/>
-      <c r="B23" s="38">
-        <v>1</v>
-      </c>
-      <c r="C23" s="38">
-        <v>0</v>
-      </c>
-      <c r="D23" s="38">
-        <v>1</v>
-      </c>
-      <c r="E23" s="38">
-        <v>1</v>
-      </c>
-      <c r="F23" s="38">
+      <c r="A23" s="25"/>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
         <f t="shared" si="13"/>
         <v>-0.1</v>
       </c>
-      <c r="G23" s="38">
+      <c r="G23">
         <f t="shared" si="14"/>
         <v>-0.1</v>
       </c>
-      <c r="H23" s="38">
+      <c r="H23">
         <f t="shared" si="15"/>
         <v>-0.1</v>
       </c>
-      <c r="I23" s="38">
+      <c r="I23">
         <f t="shared" si="16"/>
         <v>0.8</v>
       </c>
-      <c r="J23" s="38">
+      <c r="J23">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="K23" s="38">
+      <c r="K23">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L23" s="38">
+      <c r="L23">
         <f t="shared" si="19"/>
         <v>-0.1</v>
       </c>
-      <c r="M23" s="38">
+      <c r="M23">
         <f t="shared" si="20"/>
         <v>-0.1</v>
       </c>
-      <c r="N23" s="38">
+      <c r="N23">
         <f t="shared" si="21"/>
         <v>-0.1</v>
       </c>
-      <c r="O23" s="38">
-        <v>1</v>
-      </c>
-      <c r="P23" s="38">
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
         <v>0.1</v>
       </c>
       <c r="Q23" s="3">
@@ -16225,59 +16224,59 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="36"/>
-      <c r="B24" s="38">
-        <v>1</v>
-      </c>
-      <c r="C24" s="38">
-        <v>1</v>
-      </c>
-      <c r="D24" s="38">
-        <v>0</v>
-      </c>
-      <c r="E24" s="38">
-        <v>1</v>
-      </c>
-      <c r="F24" s="38">
+      <c r="A24" s="25"/>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
         <f t="shared" si="13"/>
         <v>-0.1</v>
       </c>
-      <c r="G24" s="38">
+      <c r="G24">
         <f t="shared" si="14"/>
         <v>-0.1</v>
       </c>
-      <c r="H24" s="38">
+      <c r="H24">
         <f t="shared" si="15"/>
         <v>-0.1</v>
       </c>
-      <c r="I24" s="38">
+      <c r="I24">
         <f t="shared" si="16"/>
         <v>0.8</v>
       </c>
-      <c r="J24" s="38">
+      <c r="J24">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="K24" s="38">
+      <c r="K24">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L24" s="38">
+      <c r="L24">
         <f t="shared" si="19"/>
         <v>-0.1</v>
       </c>
-      <c r="M24" s="38">
+      <c r="M24">
         <f t="shared" si="20"/>
         <v>-0.1</v>
       </c>
-      <c r="N24" s="38">
+      <c r="N24">
         <f t="shared" si="21"/>
         <v>-0.1</v>
       </c>
-      <c r="O24" s="38">
-        <v>1</v>
-      </c>
-      <c r="P24" s="38">
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
         <v>0.1</v>
       </c>
       <c r="Q24" s="3">
@@ -16285,7 +16284,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+      <c r="A25" s="26"/>
       <c r="B25" s="4">
         <v>1</v>
       </c>
@@ -16345,7 +16344,7 @@
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="35">
+      <c r="A26" s="24">
         <v>4</v>
       </c>
       <c r="B26" s="1">
@@ -16396,7 +16395,7 @@
         <f>F26+(P26*K26*D26)</f>
         <v>-0.2</v>
       </c>
-      <c r="O26" s="38">
+      <c r="O26">
         <v>1</v>
       </c>
       <c r="P26" s="1">
@@ -16407,59 +16406,59 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="36"/>
-      <c r="B27" s="38">
-        <v>0</v>
-      </c>
-      <c r="C27" s="38">
-        <v>0</v>
-      </c>
-      <c r="D27" s="38">
-        <v>1</v>
-      </c>
-      <c r="E27" s="38">
-        <v>1</v>
-      </c>
-      <c r="F27" s="38">
+      <c r="A27" s="25"/>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
         <f t="shared" si="13"/>
         <v>-0.2</v>
       </c>
-      <c r="G27" s="38">
+      <c r="G27">
         <f t="shared" si="14"/>
         <v>-0.2</v>
       </c>
-      <c r="H27" s="38">
+      <c r="H27">
         <f t="shared" si="15"/>
         <v>-0.2</v>
       </c>
-      <c r="I27" s="38">
+      <c r="I27">
         <f t="shared" ref="I27:I33" si="22">B27*F27+C27*G27+D27*H27+O27</f>
         <v>0.8</v>
       </c>
-      <c r="J27" s="38">
+      <c r="J27">
         <f t="shared" ref="J27:J33" si="23">IF(I27&gt;Q27,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K27" s="38">
+      <c r="K27">
         <f t="shared" ref="K27:K33" si="24">E27-J27</f>
         <v>0</v>
       </c>
-      <c r="L27" s="38">
+      <c r="L27">
         <f t="shared" ref="L27:L33" si="25">F27+(P27*K27*B27)</f>
         <v>-0.2</v>
       </c>
-      <c r="M27" s="38">
+      <c r="M27">
         <f t="shared" ref="M27:M33" si="26">F27+(P27*K27*C27)</f>
         <v>-0.2</v>
       </c>
-      <c r="N27" s="38">
+      <c r="N27">
         <f t="shared" ref="N27:N33" si="27">F27+(P27*K27*D27)</f>
         <v>-0.2</v>
       </c>
-      <c r="O27" s="38">
-        <v>1</v>
-      </c>
-      <c r="P27" s="38">
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27">
         <v>0.1</v>
       </c>
       <c r="Q27" s="3">
@@ -16467,59 +16466,59 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="36"/>
-      <c r="B28" s="38">
-        <v>0</v>
-      </c>
-      <c r="C28" s="38">
-        <v>1</v>
-      </c>
-      <c r="D28" s="38">
-        <v>0</v>
-      </c>
-      <c r="E28" s="38">
-        <v>1</v>
-      </c>
-      <c r="F28" s="38">
+      <c r="A28" s="25"/>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
         <f t="shared" si="13"/>
         <v>-0.2</v>
       </c>
-      <c r="G28" s="38">
+      <c r="G28">
         <f t="shared" si="14"/>
         <v>-0.2</v>
       </c>
-      <c r="H28" s="38">
+      <c r="H28">
         <f t="shared" si="15"/>
         <v>-0.2</v>
       </c>
-      <c r="I28" s="38">
+      <c r="I28">
         <f t="shared" si="22"/>
         <v>0.8</v>
       </c>
-      <c r="J28" s="38">
+      <c r="J28">
         <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="K28" s="38">
+      <c r="K28">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L28" s="38">
+      <c r="L28">
         <f t="shared" si="25"/>
         <v>-0.2</v>
       </c>
-      <c r="M28" s="38">
+      <c r="M28">
         <f t="shared" si="26"/>
         <v>-0.2</v>
       </c>
-      <c r="N28" s="38">
+      <c r="N28">
         <f t="shared" si="27"/>
         <v>-0.2</v>
       </c>
-      <c r="O28" s="38">
-        <v>1</v>
-      </c>
-      <c r="P28" s="38">
+      <c r="O28">
+        <v>1</v>
+      </c>
+      <c r="P28">
         <v>0.1</v>
       </c>
       <c r="Q28" s="3">
@@ -16527,59 +16526,59 @@
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="36"/>
-      <c r="B29" s="38">
-        <v>0</v>
-      </c>
-      <c r="C29" s="38">
-        <v>1</v>
-      </c>
-      <c r="D29" s="38">
-        <v>1</v>
-      </c>
-      <c r="E29" s="38">
-        <v>1</v>
-      </c>
-      <c r="F29" s="38">
+      <c r="A29" s="25"/>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
         <f t="shared" si="13"/>
         <v>-0.2</v>
       </c>
-      <c r="G29" s="38">
+      <c r="G29">
         <f t="shared" si="14"/>
         <v>-0.2</v>
       </c>
-      <c r="H29" s="38">
+      <c r="H29">
         <f t="shared" si="15"/>
         <v>-0.2</v>
       </c>
-      <c r="I29" s="38">
+      <c r="I29">
         <f t="shared" si="22"/>
         <v>0.6</v>
       </c>
-      <c r="J29" s="38">
+      <c r="J29">
         <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="K29" s="38">
+      <c r="K29">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L29" s="38">
+      <c r="L29">
         <f t="shared" si="25"/>
         <v>-0.2</v>
       </c>
-      <c r="M29" s="38">
+      <c r="M29">
         <f t="shared" si="26"/>
         <v>-0.2</v>
       </c>
-      <c r="N29" s="38">
+      <c r="N29">
         <f t="shared" si="27"/>
         <v>-0.2</v>
       </c>
-      <c r="O29" s="38">
-        <v>1</v>
-      </c>
-      <c r="P29" s="38">
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29">
         <v>0.1</v>
       </c>
       <c r="Q29" s="3">
@@ -16587,59 +16586,59 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="38">
-        <v>1</v>
-      </c>
-      <c r="C30" s="38">
-        <v>0</v>
-      </c>
-      <c r="D30" s="38">
-        <v>0</v>
-      </c>
-      <c r="E30" s="38">
-        <v>1</v>
-      </c>
-      <c r="F30" s="38">
+      <c r="A30" s="25"/>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
         <f t="shared" si="13"/>
         <v>-0.2</v>
       </c>
-      <c r="G30" s="38">
+      <c r="G30">
         <f t="shared" si="14"/>
         <v>-0.2</v>
       </c>
-      <c r="H30" s="38">
+      <c r="H30">
         <f t="shared" si="15"/>
         <v>-0.2</v>
       </c>
-      <c r="I30" s="38">
+      <c r="I30">
         <f t="shared" si="22"/>
         <v>0.8</v>
       </c>
-      <c r="J30" s="38">
+      <c r="J30">
         <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="K30" s="38">
+      <c r="K30">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L30" s="38">
+      <c r="L30">
         <f t="shared" si="25"/>
         <v>-0.2</v>
       </c>
-      <c r="M30" s="38">
+      <c r="M30">
         <f t="shared" si="26"/>
         <v>-0.2</v>
       </c>
-      <c r="N30" s="38">
+      <c r="N30">
         <f t="shared" si="27"/>
         <v>-0.2</v>
       </c>
-      <c r="O30" s="38">
-        <v>1</v>
-      </c>
-      <c r="P30" s="38">
+      <c r="O30">
+        <v>1</v>
+      </c>
+      <c r="P30">
         <v>0.1</v>
       </c>
       <c r="Q30" s="3">
@@ -16647,59 +16646,59 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="36"/>
-      <c r="B31" s="38">
-        <v>1</v>
-      </c>
-      <c r="C31" s="38">
-        <v>0</v>
-      </c>
-      <c r="D31" s="38">
-        <v>1</v>
-      </c>
-      <c r="E31" s="38">
-        <v>1</v>
-      </c>
-      <c r="F31" s="38">
+      <c r="A31" s="25"/>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
         <f t="shared" si="13"/>
         <v>-0.2</v>
       </c>
-      <c r="G31" s="38">
+      <c r="G31">
         <f t="shared" si="14"/>
         <v>-0.2</v>
       </c>
-      <c r="H31" s="38">
+      <c r="H31">
         <f t="shared" si="15"/>
         <v>-0.2</v>
       </c>
-      <c r="I31" s="38">
+      <c r="I31">
         <f t="shared" si="22"/>
         <v>0.6</v>
       </c>
-      <c r="J31" s="38">
+      <c r="J31">
         <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="K31" s="38">
+      <c r="K31">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L31" s="38">
+      <c r="L31">
         <f t="shared" si="25"/>
         <v>-0.2</v>
       </c>
-      <c r="M31" s="38">
+      <c r="M31">
         <f t="shared" si="26"/>
         <v>-0.2</v>
       </c>
-      <c r="N31" s="38">
+      <c r="N31">
         <f t="shared" si="27"/>
         <v>-0.2</v>
       </c>
-      <c r="O31" s="38">
-        <v>1</v>
-      </c>
-      <c r="P31" s="38">
+      <c r="O31">
+        <v>1</v>
+      </c>
+      <c r="P31">
         <v>0.1</v>
       </c>
       <c r="Q31" s="3">
@@ -16707,59 +16706,59 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="36"/>
-      <c r="B32" s="38">
-        <v>1</v>
-      </c>
-      <c r="C32" s="38">
-        <v>1</v>
-      </c>
-      <c r="D32" s="38">
-        <v>0</v>
-      </c>
-      <c r="E32" s="38">
-        <v>1</v>
-      </c>
-      <c r="F32" s="38">
+      <c r="A32" s="25"/>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
         <f t="shared" si="13"/>
         <v>-0.2</v>
       </c>
-      <c r="G32" s="38">
+      <c r="G32">
         <f t="shared" si="14"/>
         <v>-0.2</v>
       </c>
-      <c r="H32" s="38">
+      <c r="H32">
         <f t="shared" si="15"/>
         <v>-0.2</v>
       </c>
-      <c r="I32" s="38">
+      <c r="I32">
         <f t="shared" si="22"/>
         <v>0.6</v>
       </c>
-      <c r="J32" s="38">
+      <c r="J32">
         <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="K32" s="38">
+      <c r="K32">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L32" s="38">
+      <c r="L32">
         <f t="shared" si="25"/>
         <v>-0.2</v>
       </c>
-      <c r="M32" s="38">
+      <c r="M32">
         <f t="shared" si="26"/>
         <v>-0.2</v>
       </c>
-      <c r="N32" s="38">
+      <c r="N32">
         <f t="shared" si="27"/>
         <v>-0.2</v>
       </c>
-      <c r="O32" s="38">
-        <v>1</v>
-      </c>
-      <c r="P32" s="38">
+      <c r="O32">
+        <v>1</v>
+      </c>
+      <c r="P32">
         <v>0.1</v>
       </c>
       <c r="Q32" s="3">
@@ -16767,7 +16766,7 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+      <c r="A33" s="26"/>
       <c r="B33" s="4">
         <v>1</v>
       </c>
@@ -16892,7 +16891,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="21">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -16941,7 +16940,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
+      <c r="A3" s="19"/>
       <c r="B3">
         <v>0</v>
       </c>
@@ -16990,7 +16989,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
+      <c r="A4" s="19"/>
       <c r="B4">
         <v>1</v>
       </c>
@@ -17039,7 +17038,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
+      <c r="A5" s="20"/>
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -17088,8 +17087,8 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
-        <v>1</v>
+      <c r="A6" s="18">
+        <v>2</v>
       </c>
       <c r="B6" s="1">
         <v>0</v>
@@ -17139,7 +17138,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
+      <c r="A7" s="19"/>
       <c r="B7">
         <v>0</v>
       </c>
@@ -17188,7 +17187,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
+      <c r="A8" s="19"/>
       <c r="B8">
         <v>1</v>
       </c>
@@ -17237,7 +17236,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
+      <c r="A9" s="20"/>
       <c r="B9" s="4">
         <v>1</v>
       </c>
@@ -17286,8 +17285,8 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
-        <v>1</v>
+      <c r="A10" s="18">
+        <v>3</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
@@ -17337,7 +17336,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
+      <c r="A11" s="19"/>
       <c r="B11">
         <v>0</v>
       </c>
@@ -17386,7 +17385,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12">
         <v>1</v>
       </c>
@@ -17435,7 +17434,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="23"/>
+      <c r="A13" s="20"/>
       <c r="B13" s="4">
         <v>1</v>
       </c>
@@ -17484,8 +17483,8 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="21">
-        <v>1</v>
+      <c r="A14" s="18">
+        <v>4</v>
       </c>
       <c r="B14" s="1">
         <v>0</v>
@@ -17535,7 +17534,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
+      <c r="A15" s="19"/>
       <c r="B15">
         <v>0</v>
       </c>
@@ -17584,7 +17583,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
+      <c r="A16" s="19"/>
       <c r="B16">
         <v>1</v>
       </c>
@@ -17633,7 +17632,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="22"/>
+      <c r="A17" s="19"/>
       <c r="B17">
         <v>1</v>
       </c>
@@ -17682,8 +17681,8 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="21">
-        <v>1</v>
+      <c r="A18" s="18">
+        <v>5</v>
       </c>
       <c r="B18" s="1">
         <v>0</v>
@@ -17733,7 +17732,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="22"/>
+      <c r="A19" s="19"/>
       <c r="B19">
         <v>0</v>
       </c>
@@ -17782,7 +17781,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="22"/>
+      <c r="A20" s="19"/>
       <c r="B20">
         <v>1</v>
       </c>
@@ -17831,7 +17830,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="23"/>
+      <c r="A21" s="20"/>
       <c r="B21" s="4">
         <v>1</v>
       </c>
@@ -17950,7 +17949,7 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="18">
+      <c r="A2" s="35">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -17998,7 +17997,7 @@
         <f>F2+(P2*K2*D2)</f>
         <v>0.1</v>
       </c>
-      <c r="O2" s="38">
+      <c r="O2">
         <v>1</v>
       </c>
       <c r="P2" s="1">
@@ -18009,7 +18008,7 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
+      <c r="A3" s="36"/>
       <c r="B3">
         <v>0</v>
       </c>
@@ -18058,7 +18057,7 @@
         <f t="shared" ref="N3:N9" si="5">F3+(P3*K3*D3)</f>
         <v>0</v>
       </c>
-      <c r="O3" s="38">
+      <c r="O3">
         <v>1</v>
       </c>
       <c r="P3">
@@ -18069,7 +18068,7 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="19"/>
+      <c r="A4" s="36"/>
       <c r="B4">
         <v>0</v>
       </c>
@@ -18118,7 +18117,7 @@
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4">
         <v>1</v>
       </c>
       <c r="P4">
@@ -18129,7 +18128,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
+      <c r="A5" s="36"/>
       <c r="B5">
         <v>0</v>
       </c>
@@ -18178,7 +18177,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O5" s="38">
+      <c r="O5">
         <v>1</v>
       </c>
       <c r="P5">
@@ -18189,7 +18188,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="19"/>
+      <c r="A6" s="36"/>
       <c r="B6">
         <v>1</v>
       </c>
@@ -18238,7 +18237,7 @@
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
-      <c r="O6" s="38">
+      <c r="O6">
         <v>1</v>
       </c>
       <c r="P6">
@@ -18249,7 +18248,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
+      <c r="A7" s="36"/>
       <c r="B7">
         <v>1</v>
       </c>
@@ -18298,7 +18297,7 @@
         <f t="shared" si="5"/>
         <v>-0.1</v>
       </c>
-      <c r="O7" s="38">
+      <c r="O7">
         <v>1</v>
       </c>
       <c r="P7">
@@ -18309,7 +18308,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
+      <c r="A8" s="36"/>
       <c r="B8">
         <v>1</v>
       </c>
@@ -18358,7 +18357,7 @@
         <f t="shared" si="5"/>
         <v>-0.1</v>
       </c>
-      <c r="O8" s="38">
+      <c r="O8">
         <v>1</v>
       </c>
       <c r="P8">
@@ -18369,59 +18368,59 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="38">
-        <v>1</v>
-      </c>
-      <c r="C9" s="38">
-        <v>1</v>
-      </c>
-      <c r="D9" s="38">
+      <c r="A9" s="36"/>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="38">
+      <c r="F9">
         <f t="shared" si="6"/>
         <v>-0.2</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9">
         <f t="shared" si="6"/>
         <v>-0.2</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9">
         <f t="shared" si="6"/>
         <v>-0.1</v>
       </c>
-      <c r="I9" s="38">
+      <c r="I9">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="J9" s="38">
+      <c r="J9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K9" s="38">
+      <c r="K9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L9" s="38">
+      <c r="L9">
         <f t="shared" si="3"/>
         <v>-0.2</v>
       </c>
-      <c r="M9" s="38">
+      <c r="M9">
         <f t="shared" si="4"/>
         <v>-0.2</v>
       </c>
-      <c r="N9" s="38">
+      <c r="N9">
         <f t="shared" si="5"/>
         <v>-0.2</v>
       </c>
       <c r="O9" s="4">
         <v>1</v>
       </c>
-      <c r="P9" s="38">
+      <c r="P9">
         <v>0.1</v>
       </c>
       <c r="Q9" s="3">
@@ -18429,7 +18428,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="35">
+      <c r="A10" s="24">
         <v>2</v>
       </c>
       <c r="B10" s="1">
@@ -18480,7 +18479,7 @@
         <f>F10+(P10*K10*D10)</f>
         <v>-0.2</v>
       </c>
-      <c r="O10" s="38">
+      <c r="O10">
         <v>1</v>
       </c>
       <c r="P10" s="1">
@@ -18491,59 +18490,59 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="38">
-        <v>0</v>
-      </c>
-      <c r="C11" s="38">
-        <v>0</v>
-      </c>
-      <c r="D11" s="38">
-        <v>1</v>
-      </c>
-      <c r="E11" s="38">
-        <v>0</v>
-      </c>
-      <c r="F11" s="38">
+      <c r="A11" s="25"/>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <f t="shared" si="6"/>
         <v>-0.2</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11">
         <f t="shared" si="6"/>
         <v>-0.2</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11">
         <f t="shared" si="6"/>
         <v>-0.2</v>
       </c>
-      <c r="I11" s="38">
+      <c r="I11">
         <f t="shared" ref="I11:I17" si="7">B11*F11+C11*G11+D11*H11+O11</f>
         <v>0.8</v>
       </c>
-      <c r="J11" s="38">
+      <c r="J11">
         <f t="shared" ref="J11:J17" si="8">IF(I11&gt;Q11,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K11" s="38">
+      <c r="K11">
         <f t="shared" ref="K11:K17" si="9">E11-J11</f>
         <v>-1</v>
       </c>
-      <c r="L11" s="38">
+      <c r="L11">
         <f t="shared" ref="L11:L17" si="10">F11+(P11*K11*B11)</f>
         <v>-0.2</v>
       </c>
-      <c r="M11" s="38">
+      <c r="M11">
         <f t="shared" ref="M11:M17" si="11">F11+(P11*K11*C11)</f>
         <v>-0.2</v>
       </c>
-      <c r="N11" s="38">
+      <c r="N11">
         <f t="shared" ref="N11:N17" si="12">F11+(P11*K11*D11)</f>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="O11" s="38">
-        <v>1</v>
-      </c>
-      <c r="P11" s="38">
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
         <v>0.1</v>
       </c>
       <c r="Q11" s="3">
@@ -18551,59 +18550,59 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
-      <c r="B12" s="38">
-        <v>0</v>
-      </c>
-      <c r="C12" s="38">
-        <v>1</v>
-      </c>
-      <c r="D12" s="38">
-        <v>0</v>
-      </c>
-      <c r="E12" s="38">
-        <v>0</v>
-      </c>
-      <c r="F12" s="38">
+      <c r="A12" s="25"/>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <f t="shared" si="6"/>
         <v>-0.2</v>
       </c>
-      <c r="G12" s="38">
+      <c r="G12">
         <f t="shared" si="6"/>
         <v>-0.2</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12">
         <f t="shared" si="6"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="I12" s="38">
+      <c r="I12">
         <f t="shared" si="7"/>
         <v>0.8</v>
       </c>
-      <c r="J12" s="38">
+      <c r="J12">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K12" s="38">
+      <c r="K12">
         <f t="shared" si="9"/>
         <v>-1</v>
       </c>
-      <c r="L12" s="38">
+      <c r="L12">
         <f t="shared" si="10"/>
         <v>-0.2</v>
       </c>
-      <c r="M12" s="38">
+      <c r="M12">
         <f t="shared" si="11"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="N12" s="38">
+      <c r="N12">
         <f t="shared" si="12"/>
         <v>-0.2</v>
       </c>
-      <c r="O12" s="38">
-        <v>1</v>
-      </c>
-      <c r="P12" s="38">
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
         <v>0.1</v>
       </c>
       <c r="Q12" s="3">
@@ -18611,59 +18610,59 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="38">
-        <v>0</v>
-      </c>
-      <c r="C13" s="38">
-        <v>1</v>
-      </c>
-      <c r="D13" s="38">
-        <v>1</v>
-      </c>
-      <c r="E13" s="38">
-        <v>0</v>
-      </c>
-      <c r="F13" s="38">
+      <c r="A13" s="25"/>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
         <f t="shared" si="6"/>
         <v>-0.2</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13">
         <f t="shared" si="6"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13">
         <f t="shared" si="6"/>
         <v>-0.2</v>
       </c>
-      <c r="I13" s="38">
+      <c r="I13">
         <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
-      <c r="J13" s="38">
+      <c r="J13">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K13" s="38">
+      <c r="K13">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L13" s="38">
+      <c r="L13">
         <f t="shared" si="10"/>
         <v>-0.2</v>
       </c>
-      <c r="M13" s="38">
+      <c r="M13">
         <f t="shared" si="11"/>
         <v>-0.2</v>
       </c>
-      <c r="N13" s="38">
+      <c r="N13">
         <f t="shared" si="12"/>
         <v>-0.2</v>
       </c>
-      <c r="O13" s="38">
-        <v>1</v>
-      </c>
-      <c r="P13" s="38">
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
         <v>0.1</v>
       </c>
       <c r="Q13" s="3">
@@ -18671,59 +18670,59 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
-      <c r="B14" s="38">
-        <v>1</v>
-      </c>
-      <c r="C14" s="38">
-        <v>0</v>
-      </c>
-      <c r="D14" s="38">
-        <v>0</v>
-      </c>
-      <c r="E14" s="38">
-        <v>0</v>
-      </c>
-      <c r="F14" s="38">
+      <c r="A14" s="25"/>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <f t="shared" si="6"/>
         <v>-0.2</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14">
         <f t="shared" si="6"/>
         <v>-0.2</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14">
         <f t="shared" si="6"/>
         <v>-0.2</v>
       </c>
-      <c r="I14" s="38">
+      <c r="I14">
         <f t="shared" si="7"/>
         <v>0.8</v>
       </c>
-      <c r="J14" s="38">
+      <c r="J14">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K14" s="38">
+      <c r="K14">
         <f t="shared" si="9"/>
         <v>-1</v>
       </c>
-      <c r="L14" s="38">
+      <c r="L14">
         <f t="shared" si="10"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="M14" s="38">
+      <c r="M14">
         <f t="shared" si="11"/>
         <v>-0.2</v>
       </c>
-      <c r="N14" s="38">
+      <c r="N14">
         <f t="shared" si="12"/>
         <v>-0.2</v>
       </c>
-      <c r="O14" s="38">
-        <v>1</v>
-      </c>
-      <c r="P14" s="38">
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
         <v>0.1</v>
       </c>
       <c r="Q14" s="3">
@@ -18731,59 +18730,59 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="36"/>
-      <c r="B15" s="38">
-        <v>1</v>
-      </c>
-      <c r="C15" s="38">
-        <v>0</v>
-      </c>
-      <c r="D15" s="38">
-        <v>1</v>
-      </c>
-      <c r="E15" s="38">
-        <v>0</v>
-      </c>
-      <c r="F15" s="38">
+      <c r="A15" s="25"/>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
         <f t="shared" si="6"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="G15" s="38">
+      <c r="G15">
         <f t="shared" si="6"/>
         <v>-0.2</v>
       </c>
-      <c r="H15" s="38">
+      <c r="H15">
         <f t="shared" si="6"/>
         <v>-0.2</v>
       </c>
-      <c r="I15" s="38">
+      <c r="I15">
         <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
-      <c r="J15" s="38">
+      <c r="J15">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K15" s="38">
+      <c r="K15">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L15" s="38">
+      <c r="L15">
         <f t="shared" si="10"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="M15" s="38">
+      <c r="M15">
         <f t="shared" si="11"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="N15" s="38">
+      <c r="N15">
         <f t="shared" si="12"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="O15" s="38">
-        <v>1</v>
-      </c>
-      <c r="P15" s="38">
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
         <v>0.1</v>
       </c>
       <c r="Q15" s="3">
@@ -18791,59 +18790,59 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
-      <c r="B16" s="38">
-        <v>1</v>
-      </c>
-      <c r="C16" s="38">
-        <v>1</v>
-      </c>
-      <c r="D16" s="38">
-        <v>0</v>
-      </c>
-      <c r="E16" s="38">
-        <v>0</v>
-      </c>
-      <c r="F16" s="38">
+      <c r="A16" s="25"/>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <f t="shared" si="6"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="G16" s="38">
+      <c r="G16">
         <f t="shared" si="6"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16">
         <f t="shared" si="6"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="I16" s="38">
+      <c r="I16">
         <f t="shared" si="7"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="J16" s="38">
+      <c r="J16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K16" s="38">
+      <c r="K16">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L16" s="38">
+      <c r="L16">
         <f t="shared" si="10"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="M16" s="38">
+      <c r="M16">
         <f t="shared" si="11"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="N16" s="38">
+      <c r="N16">
         <f t="shared" si="12"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="O16" s="38">
-        <v>1</v>
-      </c>
-      <c r="P16" s="38">
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
         <v>0.1</v>
       </c>
       <c r="Q16" s="3">
@@ -18851,7 +18850,7 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="26"/>
       <c r="B17" s="4">
         <v>1</v>
       </c>
@@ -18861,7 +18860,7 @@
       <c r="D17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="38">
+      <c r="E17">
         <v>0</v>
       </c>
       <c r="F17" s="4">
@@ -18911,7 +18910,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="35">
+      <c r="A18" s="24">
         <v>3</v>
       </c>
       <c r="B18" s="1">
@@ -18962,7 +18961,7 @@
         <f>F18+(P18*K18*D18)</f>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="O18" s="38">
+      <c r="O18">
         <v>1</v>
       </c>
       <c r="P18" s="1">
@@ -18973,59 +18972,59 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
-      <c r="B19" s="38">
-        <v>0</v>
-      </c>
-      <c r="C19" s="38">
-        <v>0</v>
-      </c>
-      <c r="D19" s="38">
-        <v>1</v>
-      </c>
-      <c r="E19" s="38">
-        <v>0</v>
-      </c>
-      <c r="F19" s="38">
+      <c r="A19" s="25"/>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
         <f t="shared" si="13"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="G19" s="38">
+      <c r="G19">
         <f t="shared" si="14"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="H19" s="38">
+      <c r="H19">
         <f t="shared" si="15"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="I19" s="38">
+      <c r="I19">
         <f t="shared" ref="I19:I25" si="16">B19*F19+C19*G19+D19*H19+O19</f>
         <v>0.7</v>
       </c>
-      <c r="J19" s="38">
+      <c r="J19">
         <f t="shared" ref="J19:J25" si="17">IF(I19&gt;Q19,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K19" s="38">
+      <c r="K19">
         <f t="shared" ref="K19:K25" si="18">E19-J19</f>
         <v>-1</v>
       </c>
-      <c r="L19" s="38">
+      <c r="L19">
         <f t="shared" ref="L19:L25" si="19">F19+(P19*K19*B19)</f>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="M19" s="38">
+      <c r="M19">
         <f t="shared" ref="M19:M25" si="20">F19+(P19*K19*C19)</f>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="N19" s="38">
+      <c r="N19">
         <f t="shared" ref="N19:N25" si="21">F19+(P19*K19*D19)</f>
         <v>-0.4</v>
       </c>
-      <c r="O19" s="38">
-        <v>1</v>
-      </c>
-      <c r="P19" s="38">
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
         <v>0.1</v>
       </c>
       <c r="Q19" s="3">
@@ -19033,59 +19032,59 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="36"/>
-      <c r="B20" s="38">
-        <v>0</v>
-      </c>
-      <c r="C20" s="38">
-        <v>1</v>
-      </c>
-      <c r="D20" s="38">
-        <v>0</v>
-      </c>
-      <c r="E20" s="38">
-        <v>0</v>
-      </c>
-      <c r="F20" s="38">
+      <c r="A20" s="25"/>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <f t="shared" si="13"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="G20" s="38">
+      <c r="G20">
         <f t="shared" si="14"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="H20" s="38">
+      <c r="H20">
         <f t="shared" si="15"/>
         <v>-0.4</v>
       </c>
-      <c r="I20" s="38">
+      <c r="I20">
         <f t="shared" si="16"/>
         <v>0.7</v>
       </c>
-      <c r="J20" s="38">
+      <c r="J20">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="K20" s="38">
+      <c r="K20">
         <f t="shared" si="18"/>
         <v>-1</v>
       </c>
-      <c r="L20" s="38">
+      <c r="L20">
         <f t="shared" si="19"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="M20" s="38">
+      <c r="M20">
         <f t="shared" si="20"/>
         <v>-0.4</v>
       </c>
-      <c r="N20" s="38">
+      <c r="N20">
         <f t="shared" si="21"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="O20" s="38">
-        <v>1</v>
-      </c>
-      <c r="P20" s="38">
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
         <v>0.1</v>
       </c>
       <c r="Q20" s="3">
@@ -19093,59 +19092,59 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="38">
-        <v>0</v>
-      </c>
-      <c r="C21" s="38">
-        <v>1</v>
-      </c>
-      <c r="D21" s="38">
-        <v>1</v>
-      </c>
-      <c r="E21" s="38">
-        <v>0</v>
-      </c>
-      <c r="F21" s="38">
+      <c r="A21" s="25"/>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
         <f t="shared" si="13"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="G21" s="38">
+      <c r="G21">
         <f t="shared" si="14"/>
         <v>-0.4</v>
       </c>
-      <c r="H21" s="38">
+      <c r="H21">
         <f t="shared" si="15"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="I21" s="38">
+      <c r="I21">
         <f t="shared" si="16"/>
         <v>0.29999999999999993</v>
       </c>
-      <c r="J21" s="38">
+      <c r="J21">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K21" s="38">
+      <c r="K21">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L21" s="38">
+      <c r="L21">
         <f t="shared" si="19"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="M21" s="38">
+      <c r="M21">
         <f t="shared" si="20"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="N21" s="38">
+      <c r="N21">
         <f t="shared" si="21"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="O21" s="38">
-        <v>1</v>
-      </c>
-      <c r="P21" s="38">
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
         <v>0.1</v>
       </c>
       <c r="Q21" s="3">
@@ -19153,59 +19152,59 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="36"/>
-      <c r="B22" s="38">
-        <v>1</v>
-      </c>
-      <c r="C22" s="38">
-        <v>0</v>
-      </c>
-      <c r="D22" s="38">
-        <v>0</v>
-      </c>
-      <c r="E22" s="38">
-        <v>0</v>
-      </c>
-      <c r="F22" s="38">
+      <c r="A22" s="25"/>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
         <f t="shared" si="13"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="G22" s="38">
+      <c r="G22">
         <f t="shared" si="14"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="H22" s="38">
+      <c r="H22">
         <f t="shared" si="15"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="I22" s="38">
+      <c r="I22">
         <f t="shared" si="16"/>
         <v>0.7</v>
       </c>
-      <c r="J22" s="38">
+      <c r="J22">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="K22" s="38">
+      <c r="K22">
         <f t="shared" si="18"/>
         <v>-1</v>
       </c>
-      <c r="L22" s="38">
+      <c r="L22">
         <f t="shared" si="19"/>
         <v>-0.4</v>
       </c>
-      <c r="M22" s="38">
+      <c r="M22">
         <f t="shared" si="20"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="N22" s="38">
+      <c r="N22">
         <f t="shared" si="21"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="O22" s="38">
-        <v>1</v>
-      </c>
-      <c r="P22" s="38">
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
         <v>0.1</v>
       </c>
       <c r="Q22" s="3">
@@ -19213,59 +19212,59 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="36"/>
-      <c r="B23" s="38">
-        <v>1</v>
-      </c>
-      <c r="C23" s="38">
-        <v>0</v>
-      </c>
-      <c r="D23" s="38">
-        <v>1</v>
-      </c>
-      <c r="E23" s="38">
-        <v>0</v>
-      </c>
-      <c r="F23" s="38">
+      <c r="A23" s="25"/>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
         <f t="shared" si="13"/>
         <v>-0.4</v>
       </c>
-      <c r="G23" s="38">
+      <c r="G23">
         <f t="shared" si="14"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="H23" s="38">
+      <c r="H23">
         <f t="shared" si="15"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="I23" s="38">
+      <c r="I23">
         <f t="shared" si="16"/>
         <v>0.29999999999999993</v>
       </c>
-      <c r="J23" s="38">
+      <c r="J23">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K23" s="38">
+      <c r="K23">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L23" s="38">
+      <c r="L23">
         <f t="shared" si="19"/>
         <v>-0.4</v>
       </c>
-      <c r="M23" s="38">
+      <c r="M23">
         <f t="shared" si="20"/>
         <v>-0.4</v>
       </c>
-      <c r="N23" s="38">
+      <c r="N23">
         <f t="shared" si="21"/>
         <v>-0.4</v>
       </c>
-      <c r="O23" s="38">
-        <v>1</v>
-      </c>
-      <c r="P23" s="38">
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
         <v>0.1</v>
       </c>
       <c r="Q23" s="3">
@@ -19273,59 +19272,59 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="36"/>
-      <c r="B24" s="38">
-        <v>1</v>
-      </c>
-      <c r="C24" s="38">
-        <v>1</v>
-      </c>
-      <c r="D24" s="38">
-        <v>0</v>
-      </c>
-      <c r="E24" s="38">
-        <v>0</v>
-      </c>
-      <c r="F24" s="38">
+      <c r="A24" s="25"/>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
         <f t="shared" si="13"/>
         <v>-0.4</v>
       </c>
-      <c r="G24" s="38">
+      <c r="G24">
         <f t="shared" si="14"/>
         <v>-0.4</v>
       </c>
-      <c r="H24" s="38">
+      <c r="H24">
         <f t="shared" si="15"/>
         <v>-0.4</v>
       </c>
-      <c r="I24" s="38">
+      <c r="I24">
         <f t="shared" si="16"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="J24" s="38">
+      <c r="J24">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K24" s="38">
+      <c r="K24">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L24" s="38">
+      <c r="L24">
         <f t="shared" si="19"/>
         <v>-0.4</v>
       </c>
-      <c r="M24" s="38">
+      <c r="M24">
         <f t="shared" si="20"/>
         <v>-0.4</v>
       </c>
-      <c r="N24" s="38">
+      <c r="N24">
         <f t="shared" si="21"/>
         <v>-0.4</v>
       </c>
-      <c r="O24" s="38">
-        <v>1</v>
-      </c>
-      <c r="P24" s="38">
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
         <v>0.1</v>
       </c>
       <c r="Q24" s="3">
@@ -19333,7 +19332,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+      <c r="A25" s="26"/>
       <c r="B25" s="4">
         <v>1</v>
       </c>
@@ -19343,7 +19342,7 @@
       <c r="D25" s="4">
         <v>1</v>
       </c>
-      <c r="E25" s="38">
+      <c r="E25">
         <v>0</v>
       </c>
       <c r="F25" s="4">
@@ -19393,7 +19392,7 @@
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="35">
+      <c r="A26" s="24">
         <v>4</v>
       </c>
       <c r="B26" s="1">
@@ -19444,7 +19443,7 @@
         <f>F26+(P26*K26*D26)</f>
         <v>-0.4</v>
       </c>
-      <c r="O26" s="38">
+      <c r="O26">
         <v>1</v>
       </c>
       <c r="P26" s="1">
@@ -19455,59 +19454,59 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="36"/>
-      <c r="B27" s="38">
-        <v>0</v>
-      </c>
-      <c r="C27" s="38">
-        <v>0</v>
-      </c>
-      <c r="D27" s="38">
-        <v>1</v>
-      </c>
-      <c r="E27" s="38">
-        <v>0</v>
-      </c>
-      <c r="F27" s="38">
+      <c r="A27" s="25"/>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
         <f t="shared" si="13"/>
         <v>-0.4</v>
       </c>
-      <c r="G27" s="38">
+      <c r="G27">
         <f t="shared" si="14"/>
         <v>-0.4</v>
       </c>
-      <c r="H27" s="38">
+      <c r="H27">
         <f t="shared" si="15"/>
         <v>-0.4</v>
       </c>
-      <c r="I27" s="38">
+      <c r="I27">
         <f t="shared" ref="I27:I33" si="22">B27*F27+C27*G27+D27*H27+O27</f>
         <v>0.6</v>
       </c>
-      <c r="J27" s="38">
+      <c r="J27">
         <f t="shared" ref="J27:J33" si="23">IF(I27&gt;Q27,1,0)</f>
         <v>1</v>
       </c>
-      <c r="K27" s="38">
+      <c r="K27">
         <f t="shared" ref="K27:K33" si="24">E27-J27</f>
         <v>-1</v>
       </c>
-      <c r="L27" s="38">
+      <c r="L27">
         <f t="shared" ref="L27:L33" si="25">F27+(P27*K27*B27)</f>
         <v>-0.4</v>
       </c>
-      <c r="M27" s="38">
+      <c r="M27">
         <f t="shared" ref="M27:M33" si="26">F27+(P27*K27*C27)</f>
         <v>-0.4</v>
       </c>
-      <c r="N27" s="38">
+      <c r="N27">
         <f t="shared" ref="N27:N33" si="27">F27+(P27*K27*D27)</f>
         <v>-0.5</v>
       </c>
-      <c r="O27" s="38">
-        <v>1</v>
-      </c>
-      <c r="P27" s="38">
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27">
         <v>0.1</v>
       </c>
       <c r="Q27" s="3">
@@ -19515,59 +19514,59 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="36"/>
-      <c r="B28" s="38">
-        <v>0</v>
-      </c>
-      <c r="C28" s="38">
-        <v>1</v>
-      </c>
-      <c r="D28" s="38">
-        <v>0</v>
-      </c>
-      <c r="E28" s="38">
-        <v>0</v>
-      </c>
-      <c r="F28" s="38">
+      <c r="A28" s="25"/>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
         <f t="shared" si="13"/>
         <v>-0.4</v>
       </c>
-      <c r="G28" s="38">
+      <c r="G28">
         <f t="shared" si="14"/>
         <v>-0.4</v>
       </c>
-      <c r="H28" s="38">
+      <c r="H28">
         <f t="shared" si="15"/>
         <v>-0.5</v>
       </c>
-      <c r="I28" s="38">
+      <c r="I28">
         <f t="shared" si="22"/>
         <v>0.6</v>
       </c>
-      <c r="J28" s="38">
+      <c r="J28">
         <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="K28" s="38">
+      <c r="K28">
         <f t="shared" si="24"/>
         <v>-1</v>
       </c>
-      <c r="L28" s="38">
+      <c r="L28">
         <f t="shared" si="25"/>
         <v>-0.4</v>
       </c>
-      <c r="M28" s="38">
+      <c r="M28">
         <f t="shared" si="26"/>
         <v>-0.5</v>
       </c>
-      <c r="N28" s="38">
+      <c r="N28">
         <f t="shared" si="27"/>
         <v>-0.4</v>
       </c>
-      <c r="O28" s="38">
-        <v>1</v>
-      </c>
-      <c r="P28" s="38">
+      <c r="O28">
+        <v>1</v>
+      </c>
+      <c r="P28">
         <v>0.1</v>
       </c>
       <c r="Q28" s="3">
@@ -19575,59 +19574,59 @@
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="36"/>
-      <c r="B29" s="38">
-        <v>0</v>
-      </c>
-      <c r="C29" s="38">
-        <v>1</v>
-      </c>
-      <c r="D29" s="38">
-        <v>1</v>
-      </c>
-      <c r="E29" s="38">
-        <v>0</v>
-      </c>
-      <c r="F29" s="38">
+      <c r="A29" s="25"/>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
         <f t="shared" si="13"/>
         <v>-0.4</v>
       </c>
-      <c r="G29" s="38">
+      <c r="G29">
         <f t="shared" si="14"/>
         <v>-0.5</v>
       </c>
-      <c r="H29" s="38">
+      <c r="H29">
         <f t="shared" si="15"/>
         <v>-0.4</v>
       </c>
-      <c r="I29" s="38">
+      <c r="I29">
         <f t="shared" si="22"/>
         <v>9.9999999999999978E-2</v>
       </c>
-      <c r="J29" s="38">
+      <c r="J29">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K29" s="38">
+      <c r="K29">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L29" s="38">
+      <c r="L29">
         <f t="shared" si="25"/>
         <v>-0.4</v>
       </c>
-      <c r="M29" s="38">
+      <c r="M29">
         <f t="shared" si="26"/>
         <v>-0.4</v>
       </c>
-      <c r="N29" s="38">
+      <c r="N29">
         <f t="shared" si="27"/>
         <v>-0.4</v>
       </c>
-      <c r="O29" s="38">
-        <v>1</v>
-      </c>
-      <c r="P29" s="38">
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29">
         <v>0.1</v>
       </c>
       <c r="Q29" s="3">
@@ -19635,59 +19634,59 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="38">
-        <v>1</v>
-      </c>
-      <c r="C30" s="38">
-        <v>0</v>
-      </c>
-      <c r="D30" s="38">
-        <v>0</v>
-      </c>
-      <c r="E30" s="38">
-        <v>0</v>
-      </c>
-      <c r="F30" s="38">
+      <c r="A30" s="25"/>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
         <f t="shared" si="13"/>
         <v>-0.4</v>
       </c>
-      <c r="G30" s="38">
+      <c r="G30">
         <f t="shared" si="14"/>
         <v>-0.4</v>
       </c>
-      <c r="H30" s="38">
+      <c r="H30">
         <f t="shared" si="15"/>
         <v>-0.4</v>
       </c>
-      <c r="I30" s="38">
+      <c r="I30">
         <f t="shared" si="22"/>
         <v>0.6</v>
       </c>
-      <c r="J30" s="38">
+      <c r="J30">
         <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="K30" s="38">
+      <c r="K30">
         <f t="shared" si="24"/>
         <v>-1</v>
       </c>
-      <c r="L30" s="38">
+      <c r="L30">
         <f t="shared" si="25"/>
         <v>-0.5</v>
       </c>
-      <c r="M30" s="38">
+      <c r="M30">
         <f t="shared" si="26"/>
         <v>-0.4</v>
       </c>
-      <c r="N30" s="38">
+      <c r="N30">
         <f t="shared" si="27"/>
         <v>-0.4</v>
       </c>
-      <c r="O30" s="38">
-        <v>1</v>
-      </c>
-      <c r="P30" s="38">
+      <c r="O30">
+        <v>1</v>
+      </c>
+      <c r="P30">
         <v>0.1</v>
       </c>
       <c r="Q30" s="3">
@@ -19695,59 +19694,59 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="36"/>
-      <c r="B31" s="38">
-        <v>1</v>
-      </c>
-      <c r="C31" s="38">
-        <v>0</v>
-      </c>
-      <c r="D31" s="38">
-        <v>1</v>
-      </c>
-      <c r="E31" s="38">
-        <v>0</v>
-      </c>
-      <c r="F31" s="38">
+      <c r="A31" s="25"/>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
         <f t="shared" si="13"/>
         <v>-0.5</v>
       </c>
-      <c r="G31" s="38">
+      <c r="G31">
         <f t="shared" si="14"/>
         <v>-0.4</v>
       </c>
-      <c r="H31" s="38">
+      <c r="H31">
         <f t="shared" si="15"/>
         <v>-0.4</v>
       </c>
-      <c r="I31" s="38">
+      <c r="I31">
         <f t="shared" si="22"/>
         <v>9.9999999999999978E-2</v>
       </c>
-      <c r="J31" s="38">
+      <c r="J31">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K31" s="38">
+      <c r="K31">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L31" s="38">
+      <c r="L31">
         <f t="shared" si="25"/>
         <v>-0.5</v>
       </c>
-      <c r="M31" s="38">
+      <c r="M31">
         <f t="shared" si="26"/>
         <v>-0.5</v>
       </c>
-      <c r="N31" s="38">
+      <c r="N31">
         <f t="shared" si="27"/>
         <v>-0.5</v>
       </c>
-      <c r="O31" s="38">
-        <v>1</v>
-      </c>
-      <c r="P31" s="38">
+      <c r="O31">
+        <v>1</v>
+      </c>
+      <c r="P31">
         <v>0.1</v>
       </c>
       <c r="Q31" s="3">
@@ -19755,59 +19754,59 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="36"/>
-      <c r="B32" s="38">
-        <v>1</v>
-      </c>
-      <c r="C32" s="38">
-        <v>1</v>
-      </c>
-      <c r="D32" s="38">
-        <v>0</v>
-      </c>
-      <c r="E32" s="38">
-        <v>0</v>
-      </c>
-      <c r="F32" s="38">
+      <c r="A32" s="25"/>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
         <f t="shared" si="13"/>
         <v>-0.5</v>
       </c>
-      <c r="G32" s="38">
+      <c r="G32">
         <f t="shared" si="14"/>
         <v>-0.5</v>
       </c>
-      <c r="H32" s="38">
+      <c r="H32">
         <f t="shared" si="15"/>
         <v>-0.5</v>
       </c>
-      <c r="I32" s="38">
+      <c r="I32">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J32" s="38">
+      <c r="J32">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K32" s="38">
+      <c r="K32">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L32" s="38">
+      <c r="L32">
         <f t="shared" si="25"/>
         <v>-0.5</v>
       </c>
-      <c r="M32" s="38">
+      <c r="M32">
         <f t="shared" si="26"/>
         <v>-0.5</v>
       </c>
-      <c r="N32" s="38">
+      <c r="N32">
         <f t="shared" si="27"/>
         <v>-0.5</v>
       </c>
-      <c r="O32" s="38">
-        <v>1</v>
-      </c>
-      <c r="P32" s="38">
+      <c r="O32">
+        <v>1</v>
+      </c>
+      <c r="P32">
         <v>0.1</v>
       </c>
       <c r="Q32" s="3">
@@ -19815,7 +19814,7 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+      <c r="A33" s="26"/>
       <c r="B33" s="4">
         <v>1</v>
       </c>
@@ -19825,7 +19824,7 @@
       <c r="D33" s="4">
         <v>1</v>
       </c>
-      <c r="E33" s="38">
+      <c r="E33">
         <v>0</v>
       </c>
       <c r="F33" s="4">
@@ -19875,7 +19874,7 @@
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="35">
+      <c r="A34" s="24">
         <v>5</v>
       </c>
       <c r="B34" s="1">
@@ -19926,7 +19925,7 @@
         <f>F34+(P34*K34*D34)</f>
         <v>-0.5</v>
       </c>
-      <c r="O34" s="38">
+      <c r="O34">
         <v>1</v>
       </c>
       <c r="P34" s="1">
@@ -19937,59 +19936,59 @@
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="36"/>
-      <c r="B35" s="38">
-        <v>0</v>
-      </c>
-      <c r="C35" s="38">
-        <v>0</v>
-      </c>
-      <c r="D35" s="38">
-        <v>1</v>
-      </c>
-      <c r="E35" s="38">
-        <v>0</v>
-      </c>
-      <c r="F35" s="38">
+      <c r="A35" s="25"/>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
         <f t="shared" si="13"/>
         <v>-0.5</v>
       </c>
-      <c r="G35" s="38">
+      <c r="G35">
         <f t="shared" si="14"/>
         <v>-0.5</v>
       </c>
-      <c r="H35" s="38">
+      <c r="H35">
         <f t="shared" si="15"/>
         <v>-0.5</v>
       </c>
-      <c r="I35" s="38">
+      <c r="I35">
         <f t="shared" ref="I35:I41" si="28">B35*F35+C35*G35+D35*H35+O35</f>
         <v>0.5</v>
       </c>
-      <c r="J35" s="38">
+      <c r="J35">
         <f t="shared" ref="J35:J41" si="29">IF(I35&gt;Q35,1,0)</f>
         <v>0</v>
       </c>
-      <c r="K35" s="38">
+      <c r="K35">
         <f t="shared" ref="K35:K41" si="30">E35-J35</f>
         <v>0</v>
       </c>
-      <c r="L35" s="38">
+      <c r="L35">
         <f t="shared" ref="L35:L41" si="31">F35+(P35*K35*B35)</f>
         <v>-0.5</v>
       </c>
-      <c r="M35" s="38">
+      <c r="M35">
         <f t="shared" ref="M35:M41" si="32">F35+(P35*K35*C35)</f>
         <v>-0.5</v>
       </c>
-      <c r="N35" s="38">
+      <c r="N35">
         <f t="shared" ref="N35:N41" si="33">F35+(P35*K35*D35)</f>
         <v>-0.5</v>
       </c>
-      <c r="O35" s="38">
-        <v>1</v>
-      </c>
-      <c r="P35" s="38">
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35">
         <v>0.1</v>
       </c>
       <c r="Q35" s="3">
@@ -19997,59 +19996,59 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36" s="36"/>
-      <c r="B36" s="38">
-        <v>0</v>
-      </c>
-      <c r="C36" s="38">
-        <v>1</v>
-      </c>
-      <c r="D36" s="38">
-        <v>0</v>
-      </c>
-      <c r="E36" s="38">
-        <v>0</v>
-      </c>
-      <c r="F36" s="38">
+      <c r="A36" s="25"/>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
         <f t="shared" si="13"/>
         <v>-0.5</v>
       </c>
-      <c r="G36" s="38">
+      <c r="G36">
         <f t="shared" si="14"/>
         <v>-0.5</v>
       </c>
-      <c r="H36" s="38">
+      <c r="H36">
         <f t="shared" si="15"/>
         <v>-0.5</v>
       </c>
-      <c r="I36" s="38">
+      <c r="I36">
         <f t="shared" si="28"/>
         <v>0.5</v>
       </c>
-      <c r="J36" s="38">
+      <c r="J36">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K36" s="38">
+      <c r="K36">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L36" s="38">
+      <c r="L36">
         <f t="shared" si="31"/>
         <v>-0.5</v>
       </c>
-      <c r="M36" s="38">
+      <c r="M36">
         <f t="shared" si="32"/>
         <v>-0.5</v>
       </c>
-      <c r="N36" s="38">
+      <c r="N36">
         <f t="shared" si="33"/>
         <v>-0.5</v>
       </c>
-      <c r="O36" s="38">
-        <v>1</v>
-      </c>
-      <c r="P36" s="38">
+      <c r="O36">
+        <v>1</v>
+      </c>
+      <c r="P36">
         <v>0.1</v>
       </c>
       <c r="Q36" s="3">
@@ -20057,59 +20056,59 @@
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A37" s="36"/>
-      <c r="B37" s="38">
-        <v>0</v>
-      </c>
-      <c r="C37" s="38">
-        <v>1</v>
-      </c>
-      <c r="D37" s="38">
-        <v>1</v>
-      </c>
-      <c r="E37" s="38">
-        <v>0</v>
-      </c>
-      <c r="F37" s="38">
+      <c r="A37" s="25"/>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
         <f t="shared" si="13"/>
         <v>-0.5</v>
       </c>
-      <c r="G37" s="38">
+      <c r="G37">
         <f t="shared" si="14"/>
         <v>-0.5</v>
       </c>
-      <c r="H37" s="38">
+      <c r="H37">
         <f t="shared" si="15"/>
         <v>-0.5</v>
       </c>
-      <c r="I37" s="38">
+      <c r="I37">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="J37" s="38">
+      <c r="J37">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K37" s="38">
+      <c r="K37">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L37" s="38">
+      <c r="L37">
         <f t="shared" si="31"/>
         <v>-0.5</v>
       </c>
-      <c r="M37" s="38">
+      <c r="M37">
         <f t="shared" si="32"/>
         <v>-0.5</v>
       </c>
-      <c r="N37" s="38">
+      <c r="N37">
         <f t="shared" si="33"/>
         <v>-0.5</v>
       </c>
-      <c r="O37" s="38">
-        <v>1</v>
-      </c>
-      <c r="P37" s="38">
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="P37">
         <v>0.1</v>
       </c>
       <c r="Q37" s="3">
@@ -20117,59 +20116,59 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A38" s="36"/>
-      <c r="B38" s="38">
-        <v>1</v>
-      </c>
-      <c r="C38" s="38">
-        <v>0</v>
-      </c>
-      <c r="D38" s="38">
-        <v>0</v>
-      </c>
-      <c r="E38" s="38">
-        <v>0</v>
-      </c>
-      <c r="F38" s="38">
+      <c r="A38" s="25"/>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
         <f t="shared" si="13"/>
         <v>-0.5</v>
       </c>
-      <c r="G38" s="38">
+      <c r="G38">
         <f t="shared" si="14"/>
         <v>-0.5</v>
       </c>
-      <c r="H38" s="38">
+      <c r="H38">
         <f t="shared" si="15"/>
         <v>-0.5</v>
       </c>
-      <c r="I38" s="38">
+      <c r="I38">
         <f t="shared" si="28"/>
         <v>0.5</v>
       </c>
-      <c r="J38" s="38">
+      <c r="J38">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K38" s="38">
+      <c r="K38">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L38" s="38">
+      <c r="L38">
         <f t="shared" si="31"/>
         <v>-0.5</v>
       </c>
-      <c r="M38" s="38">
+      <c r="M38">
         <f t="shared" si="32"/>
         <v>-0.5</v>
       </c>
-      <c r="N38" s="38">
+      <c r="N38">
         <f t="shared" si="33"/>
         <v>-0.5</v>
       </c>
-      <c r="O38" s="38">
-        <v>1</v>
-      </c>
-      <c r="P38" s="38">
+      <c r="O38">
+        <v>1</v>
+      </c>
+      <c r="P38">
         <v>0.1</v>
       </c>
       <c r="Q38" s="3">
@@ -20177,59 +20176,59 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A39" s="36"/>
-      <c r="B39" s="38">
-        <v>1</v>
-      </c>
-      <c r="C39" s="38">
-        <v>0</v>
-      </c>
-      <c r="D39" s="38">
-        <v>1</v>
-      </c>
-      <c r="E39" s="38">
-        <v>0</v>
-      </c>
-      <c r="F39" s="38">
+      <c r="A39" s="25"/>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
         <f t="shared" si="13"/>
         <v>-0.5</v>
       </c>
-      <c r="G39" s="38">
+      <c r="G39">
         <f t="shared" si="14"/>
         <v>-0.5</v>
       </c>
-      <c r="H39" s="38">
+      <c r="H39">
         <f t="shared" si="15"/>
         <v>-0.5</v>
       </c>
-      <c r="I39" s="38">
+      <c r="I39">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="J39" s="38">
+      <c r="J39">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K39" s="38">
+      <c r="K39">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L39" s="38">
+      <c r="L39">
         <f t="shared" si="31"/>
         <v>-0.5</v>
       </c>
-      <c r="M39" s="38">
+      <c r="M39">
         <f t="shared" si="32"/>
         <v>-0.5</v>
       </c>
-      <c r="N39" s="38">
+      <c r="N39">
         <f t="shared" si="33"/>
         <v>-0.5</v>
       </c>
-      <c r="O39" s="38">
-        <v>1</v>
-      </c>
-      <c r="P39" s="38">
+      <c r="O39">
+        <v>1</v>
+      </c>
+      <c r="P39">
         <v>0.1</v>
       </c>
       <c r="Q39" s="3">
@@ -20237,59 +20236,59 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A40" s="36"/>
-      <c r="B40" s="38">
-        <v>1</v>
-      </c>
-      <c r="C40" s="38">
-        <v>1</v>
-      </c>
-      <c r="D40" s="38">
-        <v>0</v>
-      </c>
-      <c r="E40" s="38">
-        <v>0</v>
-      </c>
-      <c r="F40" s="38">
+      <c r="A40" s="25"/>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
         <f t="shared" si="13"/>
         <v>-0.5</v>
       </c>
-      <c r="G40" s="38">
+      <c r="G40">
         <f t="shared" si="14"/>
         <v>-0.5</v>
       </c>
-      <c r="H40" s="38">
+      <c r="H40">
         <f t="shared" si="15"/>
         <v>-0.5</v>
       </c>
-      <c r="I40" s="38">
+      <c r="I40">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="J40" s="38">
+      <c r="J40">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K40" s="38">
+      <c r="K40">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L40" s="38">
+      <c r="L40">
         <f t="shared" si="31"/>
         <v>-0.5</v>
       </c>
-      <c r="M40" s="38">
+      <c r="M40">
         <f t="shared" si="32"/>
         <v>-0.5</v>
       </c>
-      <c r="N40" s="38">
+      <c r="N40">
         <f t="shared" si="33"/>
         <v>-0.5</v>
       </c>
-      <c r="O40" s="38">
-        <v>1</v>
-      </c>
-      <c r="P40" s="38">
+      <c r="O40">
+        <v>1</v>
+      </c>
+      <c r="P40">
         <v>0.1</v>
       </c>
       <c r="Q40" s="3">
@@ -20297,7 +20296,7 @@
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
+      <c r="A41" s="26"/>
       <c r="B41" s="4">
         <v>1</v>
       </c>
@@ -20377,22 +20376,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="29"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="34"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -20439,7 +20438,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="24">
+      <c r="A3" s="27">
         <v>1</v>
       </c>
       <c r="B3" s="1">
@@ -20488,7 +20487,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="25"/>
+      <c r="A4" s="28"/>
       <c r="B4">
         <v>0</v>
       </c>
@@ -20537,7 +20536,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="25"/>
+      <c r="A5" s="28"/>
       <c r="B5">
         <v>1</v>
       </c>
@@ -20586,7 +20585,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
+      <c r="A6" s="31"/>
       <c r="B6">
         <v>1</v>
       </c>
@@ -20635,7 +20634,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="24">
+      <c r="A7" s="27">
         <v>2</v>
       </c>
       <c r="B7" s="1">
@@ -20686,7 +20685,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="25"/>
+      <c r="A8" s="28"/>
       <c r="B8">
         <v>0</v>
       </c>
@@ -20735,7 +20734,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="25"/>
+      <c r="A9" s="28"/>
       <c r="B9">
         <v>1</v>
       </c>
@@ -20784,7 +20783,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
+      <c r="A10" s="31"/>
       <c r="B10">
         <v>1</v>
       </c>
@@ -20833,7 +20832,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="24">
+      <c r="A11" s="27">
         <v>3</v>
       </c>
       <c r="B11" s="1">
@@ -20884,7 +20883,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="25"/>
+      <c r="A12" s="28"/>
       <c r="B12">
         <v>0</v>
       </c>
@@ -20933,7 +20932,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="25"/>
+      <c r="A13" s="28"/>
       <c r="B13">
         <v>1</v>
       </c>
@@ -20982,7 +20981,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="26"/>
+      <c r="A14" s="31"/>
       <c r="B14">
         <v>1</v>
       </c>
@@ -21031,7 +21030,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="24">
+      <c r="A15" s="27">
         <v>4</v>
       </c>
       <c r="B15" s="1">
@@ -21082,7 +21081,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="25"/>
+      <c r="A16" s="28"/>
       <c r="B16">
         <v>0</v>
       </c>
@@ -21131,7 +21130,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="25"/>
+      <c r="A17" s="28"/>
       <c r="B17">
         <v>1</v>
       </c>
@@ -21180,7 +21179,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
+      <c r="A18" s="31"/>
       <c r="B18">
         <v>1</v>
       </c>
@@ -21229,7 +21228,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="24">
+      <c r="A19" s="27">
         <v>5</v>
       </c>
       <c r="B19" s="1">
@@ -21280,7 +21279,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="25"/>
+      <c r="A20" s="28"/>
       <c r="B20">
         <v>0</v>
       </c>
@@ -21329,7 +21328,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="25"/>
+      <c r="A21" s="28"/>
       <c r="B21">
         <v>1</v>
       </c>
@@ -21378,7 +21377,7 @@
       </c>
     </row>
     <row r="22" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="16">
         <v>1</v>
       </c>
@@ -21427,22 +21426,22 @@
       </c>
     </row>
     <row r="24" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-      <c r="N24" s="31"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
@@ -21489,7 +21488,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="21">
+      <c r="A26" s="18">
         <v>1</v>
       </c>
       <c r="B26" s="1">
@@ -21538,7 +21537,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="22"/>
+      <c r="A27" s="19"/>
       <c r="B27">
         <v>0</v>
       </c>
@@ -21587,7 +21586,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="22"/>
+      <c r="A28" s="19"/>
       <c r="B28">
         <v>1</v>
       </c>
@@ -21636,7 +21635,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="23"/>
+      <c r="A29" s="20"/>
       <c r="B29" s="4">
         <v>1</v>
       </c>
@@ -21685,7 +21684,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="21">
+      <c r="A30" s="18">
         <v>2</v>
       </c>
       <c r="B30" s="1">
@@ -21736,7 +21735,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="22"/>
+      <c r="A31" s="19"/>
       <c r="B31">
         <v>0</v>
       </c>
@@ -21785,7 +21784,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="22"/>
+      <c r="A32" s="19"/>
       <c r="B32">
         <v>1</v>
       </c>
@@ -21834,7 +21833,7 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="23"/>
+      <c r="A33" s="20"/>
       <c r="B33" s="4">
         <v>1</v>
       </c>
@@ -21883,7 +21882,7 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="21">
+      <c r="A34" s="18">
         <v>3</v>
       </c>
       <c r="B34" s="1">
@@ -21934,7 +21933,7 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="22"/>
+      <c r="A35" s="19"/>
       <c r="B35">
         <v>0</v>
       </c>
@@ -21983,7 +21982,7 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="22"/>
+      <c r="A36" s="19"/>
       <c r="B36">
         <v>1</v>
       </c>
@@ -22032,7 +22031,7 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="23"/>
+      <c r="A37" s="20"/>
       <c r="B37" s="4">
         <v>1</v>
       </c>
@@ -22081,7 +22080,7 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="21">
+      <c r="A38" s="18">
         <v>4</v>
       </c>
       <c r="B38" s="1">
@@ -22132,7 +22131,7 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="22"/>
+      <c r="A39" s="19"/>
       <c r="B39">
         <v>0</v>
       </c>
@@ -22181,7 +22180,7 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="22"/>
+      <c r="A40" s="19"/>
       <c r="B40">
         <v>1</v>
       </c>
@@ -22230,7 +22229,7 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="23"/>
+      <c r="A41" s="20"/>
       <c r="B41" s="4">
         <v>1</v>
       </c>
@@ -22279,7 +22278,7 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="21">
+      <c r="A42" s="18">
         <v>5</v>
       </c>
       <c r="B42" s="1">
@@ -22330,7 +22329,7 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="22"/>
+      <c r="A43" s="19"/>
       <c r="B43">
         <v>0</v>
       </c>
@@ -22379,7 +22378,7 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="22"/>
+      <c r="A44" s="19"/>
       <c r="B44">
         <v>1</v>
       </c>
@@ -22428,7 +22427,7 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="23"/>
+      <c r="A45" s="20"/>
       <c r="B45" s="4">
         <v>1</v>
       </c>
@@ -22477,22 +22476,22 @@
       </c>
     </row>
     <row r="47" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A47" s="32" t="s">
+      <c r="A47" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B47" s="33"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="33"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="33"/>
-      <c r="M47" s="33"/>
-      <c r="N47" s="34"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="22"/>
+      <c r="N47" s="23"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
@@ -22539,7 +22538,7 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="35">
+      <c r="A49" s="24">
         <v>1</v>
       </c>
       <c r="B49" s="1">
@@ -22588,7 +22587,7 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="36"/>
+      <c r="A50" s="25"/>
       <c r="B50">
         <v>1</v>
       </c>
@@ -22637,7 +22636,7 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="36"/>
+      <c r="A51" s="25"/>
       <c r="B51">
         <v>1</v>
       </c>
@@ -22686,7 +22685,7 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="37"/>
+      <c r="A52" s="26"/>
       <c r="B52" s="4">
         <v>1</v>
       </c>
@@ -22735,7 +22734,7 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="35">
+      <c r="A53" s="24">
         <v>2</v>
       </c>
       <c r="B53" s="1">
@@ -22786,7 +22785,7 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="36"/>
+      <c r="A54" s="25"/>
       <c r="B54">
         <v>1</v>
       </c>
@@ -22835,7 +22834,7 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="36"/>
+      <c r="A55" s="25"/>
       <c r="B55">
         <v>1</v>
       </c>
@@ -22884,7 +22883,7 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="37"/>
+      <c r="A56" s="26"/>
       <c r="B56" s="4">
         <v>1</v>
       </c>
@@ -22934,21 +22933,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A24:N24"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A37"/>
     <mergeCell ref="A38:A41"/>
     <mergeCell ref="A42:A45"/>
     <mergeCell ref="A47:N47"/>
     <mergeCell ref="A49:A52"/>
     <mergeCell ref="A53:A56"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A24:N24"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
